--- a/data_kr/weekly_data/sector_daily_20261027.xlsx
+++ b/data_kr/weekly_data/sector_daily_20261027.xlsx
@@ -608,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1041,14 +1041,467 @@
       </c>
       <c r="E26" s="7" t="inlineStr"/>
     </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>🌐 글로벌 코멘트 (미국장 마감)</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n"/>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>① 섹터 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+    </row>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>10.27 미국 NBI +1.9%·XBI +2.9%가 S&amp;P500 +0.6%·XLV -0.1%를 앞서 바이오 베타가 강했다. ARKG +6.0%가 상단을 이끌었다.</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="8" t="n"/>
+    </row>
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>1D는 유전자 가위 +10.7%·AI +7.3%·DNA 합성 +7.1%로 쏠리고 빅파마 +0.2%는 정체다. 20D는 진단(PCR) +23.1%·로봇 수술 +11.9%가 앞서고, PD-1xVEGF -11.9%가 가장 약하다.</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>유럽 EXV4 +0.5%는 IEUR +0.6%와 비슷했고, 일본 TOPIX 제약 -2.1%는 TOPIX +0.5%와 대조된다. 중국 바이오는 0.0%로 보합이었다.</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>글로벌 CDMO 안에서도 Lonza +13.2%(20D)와 우시 바이오 -15.4%(20D)의 격차가 커, 국내 CDMO는 수주 차별화를 따져볼 필요가 있다.</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="31" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>유전자 가위 강세가 프라임 1D +20.5% 한 종목에 기대는지 확인이 필요하다. 대만 지수는 데이터에 없어 비교에서 빠졌고, 미 10년물 4.99%는 3일간 고정이다.</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>② 종목 코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>등락</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
+        <is>
+          <t>프라임 (US)</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>+20.5%</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>그룹 내 최고 상승으로 유전자 가위 그룹 상승을 주도. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="17.5" customHeight="1">
+      <c r="A42" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t>Absci (US)</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>+11.9%</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>AI 그룹 내 상위권 급등. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr"/>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Twist (US)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>+10.1%</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>AI·DNA 합성 두 그룹에 속하며 5D +12.0%로 강세가 이어짐. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>슈뢰딩거 (US)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>+9.1%</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>1D +9.1%·5D +14.2%로 AI 그룹 강세를 이끌었으나 20D는 -8.6%. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="17.5" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>인텔리아 (US)</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>+9.1%</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>유전자 가위 그룹 상승을 동반한 급등. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>에디타스 (US)</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>+8.3%</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>가위 그룹 상승에 동반된 1D 급등. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="17.5" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>Dyne (US)</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>+7.8%</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>RNA 그룹 내 1D 최고 상승, 5D도 +4.1%. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="31" customHeight="1">
+      <c r="A48" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Tempus AI (US)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>+7.4%</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>[추정] BMS 데이터 협력 확대와 Pathos 협력 발표가 부각된 것으로 보임. 계약 금액은 미공개.</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>tempus.com 보도자료</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Summit (US)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>+5.7%</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 1026 임상 생존 혜택 보고와 루닛 병리 협력 소식이 반영된 듯. 5D는 -4.7%였다.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>크리스퍼 (CH)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>+5.0%</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>가위 그룹 상승에 동반됐으나 그룹 내에서는 상대적으로 약한 상승. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Eli Lilly (US)</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 1D는 보합이나 20D +11.4%로 빅파마 최고. 10.29 실적 발표를 앞둔 기대 반영 가능성.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>unusualwhales (실적 일정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="17.5" customHeight="1">
+      <c r="A52" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Alnylam (US)</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>헌팅틴 83%는 개인 최대치이고 평균은 60~64%다. 1D -0.4%로 주가 반응은 제한적.</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>RARE Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Akeso (CN)</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>-3.9%</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>PD-1xVEGF 그룹 약세 속에 1D -3.9%·5D -11.5%로 하락. 특이 뉴스 없음 — 섹터·수급 동반.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="17.5" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Arrowhead (US)</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>뇌척수액 타우 -73% 발표에도 1D +0.1%로 반응이 미미함. 20D는 -11.8%.</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1027)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
     <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2168,10 +2621,10 @@
         <v>-0.004585112879195423</v>
       </c>
       <c r="U19" s="22" t="n">
-        <v>0.005499517814788746</v>
+        <v>0.0327792714117953</v>
       </c>
       <c r="V19" s="22" t="n">
-        <v>-0.1376906134148145</v>
+        <v>-0.1179690925561217</v>
       </c>
     </row>
     <row r="20">
@@ -2238,10 +2691,10 @@
         <v>0.01854630780299037</v>
       </c>
       <c r="U20" s="22" t="n">
-        <v>0.004102257815514558</v>
+        <v>0.03317233151206628</v>
       </c>
       <c r="V20" s="22" t="n">
-        <v>-0.116251140544375</v>
+        <v>-0.09254526025634059</v>
       </c>
     </row>
     <row r="21">
@@ -2308,10 +2761,10 @@
         <v>0.009547128132854299</v>
       </c>
       <c r="U21" s="22" t="n">
-        <v>0.01757493688591387</v>
+        <v>0.04281425467919693</v>
       </c>
       <c r="V21" s="22" t="n">
-        <v>-0.2110425549278407</v>
+        <v>-0.1927883899335536</v>
       </c>
     </row>
     <row r="22">
@@ -2378,10 +2831,10 @@
         <v>0.01111154755888828</v>
       </c>
       <c r="U22" s="22" t="n">
-        <v>0.004657911095002667</v>
+        <v>0.02122833935937582</v>
       </c>
       <c r="V22" s="22" t="n">
-        <v>-0.05534273633805513</v>
+        <v>-0.03933509285408738</v>
       </c>
     </row>
     <row r="23">
@@ -2448,10 +2901,10 @@
         <v>-0.007212246036918341</v>
       </c>
       <c r="U23" s="22" t="n">
-        <v>0.02406215199613958</v>
+        <v>0.03929940933230031</v>
       </c>
       <c r="V23" s="22" t="n">
-        <v>-0.09759168822089509</v>
+        <v>-0.08525749971415449</v>
       </c>
     </row>
     <row r="24">
@@ -2518,10 +2971,10 @@
         <v>-0.008344874562968951</v>
       </c>
       <c r="U24" s="22" t="n">
-        <v>0.02208785504507106</v>
+        <v>0.03215367487594995</v>
       </c>
       <c r="V24" s="22" t="n">
-        <v>-0.04069600136687297</v>
+        <v>-0.03134445205615934</v>
       </c>
     </row>
     <row r="25">
@@ -2588,10 +3041,10 @@
         <v>0.003360646900885578</v>
       </c>
       <c r="U25" s="22" t="n">
-        <v>-0.009669402301262319</v>
+        <v>-0.006067391211686053</v>
       </c>
       <c r="V25" s="22" t="n">
-        <v>-0.07753411942330217</v>
+        <v>-0.07447118226395748</v>
       </c>
     </row>
     <row r="26">
@@ -2658,10 +3111,10 @@
         <v>0.0004967383909154632</v>
       </c>
       <c r="U26" s="22" t="n">
-        <v>0.01291860923929566</v>
+        <v>0.03511612061725068</v>
       </c>
       <c r="V26" s="22" t="n">
-        <v>-0.05000017033638408</v>
+        <v>-0.0324934622264525</v>
       </c>
     </row>
     <row r="27">
@@ -2728,10 +3181,10 @@
         <v>0.02166023893918193</v>
       </c>
       <c r="U27" s="22" t="n">
-        <v>0.005914802540734598</v>
+        <v>0.03483991989126738</v>
       </c>
       <c r="V27" s="22" t="n">
-        <v>-0.1359927752675782</v>
+        <v>-0.1114804446687769</v>
       </c>
     </row>
     <row r="28">
@@ -2798,10 +3251,10 @@
         <v>0.003776683295047586</v>
       </c>
       <c r="U28" s="22" t="n">
-        <v>-0.006399421775616823</v>
+        <v>0.00322135149480092</v>
       </c>
       <c r="V28" s="22" t="n">
-        <v>-0.1607337387828238</v>
+        <v>-0.1528237157814812</v>
       </c>
     </row>
     <row r="29">
@@ -2868,10 +3321,10 @@
         <v>-0.01702388769499141</v>
       </c>
       <c r="U29" s="22" t="n">
-        <v>0.02269694304576718</v>
+        <v>0.04478681481826091</v>
       </c>
       <c r="V29" s="22" t="n">
-        <v>-0.1244229069820515</v>
+        <v>-0.1083518542332686</v>
       </c>
     </row>
     <row r="30">
@@ -2938,10 +3391,10 @@
         <v>0.04536236978118032</v>
       </c>
       <c r="U30" s="22" t="n">
-        <v>0</v>
+        <v>0.04122456965109874</v>
       </c>
       <c r="V30" s="22" t="n">
-        <v>-0.06205373298439646</v>
+        <v>-0.02003378206739822</v>
       </c>
     </row>
   </sheetData>
@@ -3464,7 +3917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3939,14 +4392,459 @@
       </c>
       <c r="E28" s="7" t="inlineStr"/>
     </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>🌐 글로벌 코멘트 (미국장 마감)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>① 섹터 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>10.27 LIT +2.2%로 NASDAQ(+1.2%)와 S&amp;P500(+0.6%)을 웃돌았다. 중국 3개 지수는 모두 0.0%로 보합이었고, 일본·대만·유럽 지수 데이터는 없어 비교에서 뺐다.</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n"/>
+      <c r="D35" s="8" t="n"/>
+      <c r="E35" s="8" t="n"/>
+    </row>
+    <row r="36" ht="31" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>10.27 ESS·차세대(+10.7%)와 리튬(+4.6%)으로 자금이 들어왔고, 장비·부품(-5.1%)과 소재(-2.7%)에서는 빠졌다. 20D 누적은 리튬(-21.1%)이 여전히 가장 부진하다.</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+    </row>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1D 국가 평균은 CA(+7.5%)와 US(+6.5%)가 상위, CN(-2.3%)과 DE(-2.1%)가 하위였다. 중국 21종목 평균 하락은 같은 날 중국 지수 보합과 엇갈린다.</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+    </row>
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>중국 셀(CATL 20D -31.8%)의 약세가 이어지면 한국 셀·소재 업체의 가격·점유율 부담이 커질 수 있다. 리튬 반등은 소재 가격 기대를 개선하는 재료로 볼 수 있다.</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+    </row>
+    <row r="39" ht="31" customHeight="1">
+      <c r="A39" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>CATL의 3분기 마진 하락(20.69%, 2분기 연속 감소)이 4분기에도 이어지는지 확인해야 한다. 리튬 반등이 20D 낙폭(-21.1%)을 되돌릴 만큼 지속되는지도 체크포인트다.</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>② 종목 코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>등락</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>Tesla (US)</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 3분기 매출 280억5천만 달러와 FSD 뉴스가 반영됐다. 합병 기대 비관 투자의견(11년 만의 최저)에도 반등했다.</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(1026·1027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17.5" customHeight="1">
+      <c r="A44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
+        <is>
+          <t>GM (US)</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 완성차 그룹 평균(+0.2%) 대비 개별 강세, 원인 미확인.</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr"/>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz (DE)</t>
+        </is>
+      </c>
+      <c r="C45" s="13" t="inlineStr">
+        <is>
+          <t>-3.9%</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 원인 미확인, 5D -3.8%·20D -5.5%로 약세가 이어진다.</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Panasonic (JP)</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>+3.0%</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 1D 반등 원인 미확인, 5D -4.9%·20D -14.0%로 여전히 약세.</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr"/>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>CATL (CN)</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>-2.3%</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>10.21 3분기 실적 미스(매출 1,652억 위안, 기대 1,750억)로 급락했다. 5D -15.3%는 이 영향이 반영된 것이다.</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>Börsen-Zeitung</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="31" customHeight="1">
+      <c r="A48" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Enovix (US)</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>+25.0%</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 10.27 급등의 직접 재료는 미확인. 10.15 드론 배터리 10만 대 주문 보도 뒤 10.16에 -7.1% 되밀렸다.</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>Yahoo Finance·MarketBeat(10.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17.5" customHeight="1">
+      <c r="A49" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B49" s="12" t="inlineStr">
+        <is>
+          <t>Fluence (US)</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>+9.3%</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 1D 급등은 단기 반등 성격, 5D +1.3%·20D -20.7%.</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>QuantumScape (US)</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>+7.2%</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 5D +5.0%로 단기 반등 흐름, 20D는 -14.9%.</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr"/>
+    </row>
+    <row r="51" ht="17.5" customHeight="1">
+      <c r="A51" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Albemarle (US)</t>
+        </is>
+      </c>
+      <c r="C51" s="17" t="inlineStr">
+        <is>
+          <t>+5.9%</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 리튬 그룹(+4.6%)과 동반 강세, 20D -12.8%는 여전히 부진.</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="17.5" customHeight="1">
+      <c r="A52" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>SQM (CL)</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>+5.8%</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 리튬 그룹 동반 강세, 5D는 +0.4%에 그쳐 1D 반등 폭이 크다.</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr"/>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B53" s="12" t="inlineStr">
+        <is>
+          <t>Sigma Lithium (CA)</t>
+        </is>
+      </c>
+      <c r="C53" s="17" t="inlineStr">
+        <is>
+          <t>+7.5%</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 리튬 그룹 동반 강세, 20D -16.7%로 낙폭이 크다.</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="17.5" customHeight="1">
+      <c r="A54" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Umicore (BE)</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>+5.4%</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 1D 급등 원인 미확인, 5D +0.2%·20D -13.4%.</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr"/>
+    </row>
+    <row r="55" ht="31" customHeight="1">
+      <c r="A55" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B55" s="12" t="inlineStr">
+        <is>
+          <t>Easpring(양극) (CN)</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>-7.3%</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 1D -7.3% 원인 미확인, 5D -8.2%·20D -11.5%로 약세 지속.</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="31" customHeight="1">
+      <c r="A56" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Capchem(전해액) (CN)</t>
+        </is>
+      </c>
+      <c r="C56" s="15" t="inlineStr">
+        <is>
+          <t>-7.2%</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 1D 하락 원인 미확인, 5D -11.8%·20D -32.0%로 소재 내 20D 최저.</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="A31:E31"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4123,22 +5021,22 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>4.986000061035156</v>
+        <v>4.993000030517578</v>
       </c>
       <c r="M5" s="21" t="n">
-        <v>0</v>
+        <v>0.006999969482421875</v>
       </c>
       <c r="N5" s="21" t="n">
-        <v>-0.1310000419616699</v>
+        <v>-0.124000072479248</v>
       </c>
       <c r="O5" s="21" t="n">
-        <v>-0.1979999542236328</v>
+        <v>-0.1909999847412109</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>0.3450002670288086</v>
+        <v>0.3520002365112305</v>
       </c>
       <c r="Q5" s="21" t="n">
-        <v>0.8229999542236328</v>
+        <v>0.8299999237060547</v>
       </c>
     </row>
     <row r="6">
@@ -4181,22 +5079,22 @@
         </is>
       </c>
       <c r="L6" s="21" t="n">
-        <v>1323.969970703125</v>
+        <v>1326.81005859375</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>2.2099609375</v>
+        <v>5.050048828125</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>-6.030029296875</v>
+        <v>-3.18994140625</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>-43.3900146484375</v>
+        <v>-40.5499267578125</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>-134.0400390625</v>
+        <v>-131.199951171875</v>
       </c>
       <c r="Q6" s="21" t="n">
-        <v>-113.9400634765625</v>
+        <v>-111.0999755859375</v>
       </c>
     </row>
     <row r="7">
@@ -4239,22 +5137,22 @@
         </is>
       </c>
       <c r="L7" s="21" t="n">
-        <v>6.667500019073486</v>
+        <v>6.655799865722656</v>
       </c>
       <c r="M7" s="21" t="n">
-        <v>-0.01039981842041016</v>
+        <v>-0.02209997177124023</v>
       </c>
       <c r="N7" s="21" t="n">
-        <v>-0.02339982986450195</v>
+        <v>-0.03509998321533203</v>
       </c>
       <c r="O7" s="21" t="n">
-        <v>-0.04360008239746094</v>
+        <v>-0.05530023574829102</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>-0.1043000221252441</v>
+        <v>-0.1160001754760742</v>
       </c>
       <c r="Q7" s="21" t="n">
-        <v>-0.3285999298095703</v>
+        <v>-0.3403000831604004</v>
       </c>
     </row>
     <row r="8">
@@ -4329,22 +5227,22 @@
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>26169.380859375</v>
+        <v>26477.810546875</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>0</v>
+        <v>0.0117858992980151</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.009666648632012387</v>
+        <v>0.002005320518676745</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.03322432018910204</v>
+        <v>-0.02182999938308061</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.04962685734093997</v>
+        <v>0.06199765378205235</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0.1259526656486749</v>
+        <v>0.1392230303803419</v>
       </c>
     </row>
     <row r="11">
@@ -4359,22 +5257,22 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>7676.77001953125</v>
+        <v>7722.60009765625</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>0.005969968881235133</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-0.004641747887336178</v>
+        <v>0.001300509903457092</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.008606045059483591</v>
+        <v>-0.002687453999444034</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0.03555691855583709</v>
+        <v>0.04173916113436316</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.1214330610665766</v>
+        <v>0.1281279815435323</v>
       </c>
     </row>
     <row r="12">
@@ -4389,22 +5287,22 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>61.27000045776367</v>
+        <v>62.63000106811523</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0</v>
+        <v>0.02219684348279172</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.04667801994706311</v>
+        <v>-0.02551728116712293</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.1122862440197073</v>
+        <v>-0.09258180072069155</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>-0.107241688623086</v>
+        <v>-0.08742527211749107</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>-0.05534998641389055</v>
+        <v>-0.0343817379163025</v>
       </c>
     </row>
     <row r="13">
@@ -4419,22 +5317,22 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>3662.39208984375</v>
+        <v>3697.52001953125</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>-0.009500402838103716</v>
+        <v>0</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.01953702713633576</v>
+        <v>-0.01013289084315661</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.05811733445178502</v>
+        <v>-0.04908324218705851</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>-0.0507622044206768</v>
+        <v>-0.04165756523354636</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>-0.07721349090931684</v>
+        <v>-0.06836255992958817</v>
       </c>
     </row>
     <row r="14">
@@ -4449,22 +5347,22 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>2.582000017166138</v>
+        <v>2.651000022888184</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>-0.0444115062469288</v>
+        <v>0</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.06313498626497926</v>
+        <v>-0.03809870009971017</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.2204106313665121</v>
+        <v>-0.1995772965334645</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.2851605688408566</v>
+        <v>-0.2660575771629324</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>-0.1895794321851452</v>
+        <v>-0.1679221806573692</v>
       </c>
     </row>
     <row r="15">
@@ -4479,22 +5377,22 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>23049.8203125</v>
+        <v>23211.810546875</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>-0.00697878496155524</v>
+        <v>0</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.03426884631067872</v>
+        <v>-0.02748185127954894</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.05957830185687241</v>
+        <v>-0.05296917739393991</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>-0.08558511510392475</v>
+        <v>-0.07915876212103512</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>-0.1006892107773045</v>
+        <v>-0.09436900682139138</v>
       </c>
     </row>
     <row r="17">
@@ -4912,13 +5810,13 @@
         </is>
       </c>
       <c r="I28" s="22" t="n">
-        <v>0</v>
+        <v>0.0117858992980151</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>0</v>
+        <v>0.005969968881235133</v>
       </c>
       <c r="K28" s="22" t="n">
-        <v>0</v>
+        <v>0.02219684348279172</v>
       </c>
     </row>
     <row r="30">
@@ -5225,7 +6123,7 @@
         <v>0.001908947137856165</v>
       </c>
       <c r="C40" s="22" t="n">
-        <v>0</v>
+        <v>-0.01887486368359892</v>
       </c>
       <c r="D40" s="22" t="n">
         <v>0.005128805828580552</v>
@@ -5252,13 +6150,13 @@
         </is>
       </c>
       <c r="B41" s="22" t="n">
-        <v>-0.009500402838103716</v>
+        <v>0</v>
       </c>
       <c r="C41" s="22" t="n">
-        <v>-0.0444115062469288</v>
+        <v>0</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>-0.00697878496155524</v>
+        <v>0</v>
       </c>
       <c r="H41" s="20" t="inlineStr">
         <is>
@@ -5266,13 +6164,13 @@
         </is>
       </c>
       <c r="I41" s="21" t="n">
-        <v>4.986000061035156</v>
+        <v>4.993000030517578</v>
       </c>
       <c r="J41" s="23" t="n">
-        <v>1323.969970703125</v>
+        <v>1326.81005859375</v>
       </c>
       <c r="K41" s="21" t="n">
-        <v>6.667500019073486</v>
+        <v>6.655799865722656</v>
       </c>
     </row>
     <row r="43">
@@ -8563,11 +9461,11 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>Panasonic (JP)</t>
+          <t>Enovix (US)</t>
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>0.0296006702038536</v>
+        <v>0.2499999332783844</v>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
@@ -8575,86 +9473,86 @@
         </is>
       </c>
       <c r="F5" s="22" t="n">
-        <v>-0.02039271214175808</v>
+        <v>-0.02605735040170287</v>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>AU (1종목)</t>
+          <t>CA (1종목)</t>
         </is>
       </c>
       <c r="J5" s="22" t="n">
-        <v>0.01408457798608986</v>
+        <v>0.07506357070339242</v>
       </c>
       <c r="K5" s="22" t="n">
-        <v>0.01408457798608986</v>
+        <v>0.07506357070339242</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>Tianqi (CN)</t>
+          <t>Fluence (US)</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>0.01752921921295592</v>
+        <v>0.09272731434215209</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Li Auto (CN)</t>
+          <t>Tinci(전해액) (CN)</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>-0.02159242249755078</v>
+        <v>-0.03025883756732739</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>JP (2종목)</t>
+          <t>US (11종목)</t>
         </is>
       </c>
       <c r="J6" s="22" t="n">
-        <v>0.01239417533291814</v>
+        <v>0.06492168132510882</v>
       </c>
       <c r="K6" s="22" t="n">
-        <v>0.01239417533291814</v>
+        <v>0.05543183714146549</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Ganfeng (CN)</t>
+          <t>Sigma Lithium (CA)</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>0.01746723254120064</v>
+        <v>0.07506357070339242</v>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Tinci(전해액) (CN)</t>
+          <t>Ronbay(양극) (CN)</t>
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>-0.02442581366532182</v>
+        <v>-0.03513905912138526</v>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>BE (1종목)</t>
+          <t>CL (1종목)</t>
         </is>
       </c>
       <c r="J7" s="22" t="n">
-        <v>0</v>
+        <v>0.05845178067412937</v>
       </c>
       <c r="K7" s="22" t="n">
-        <v>0</v>
+        <v>0.05845178067412937</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Pilbara (AU)</t>
+          <t>QuantumScape (US)</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>0.01408457798608986</v>
+        <v>0.07179480157033469</v>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
@@ -8662,57 +9560,57 @@
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>-0.02989497921950657</v>
+        <v>-0.03555075833158938</v>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>CA (1종목)</t>
+          <t>BE (1종목)</t>
         </is>
       </c>
       <c r="J8" s="22" t="n">
-        <v>0</v>
+        <v>0.05379392815106199</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0</v>
+        <v>0.05379392815106199</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Rivian (US)</t>
+          <t>Lithium Americas (US)</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0</v>
+        <v>0.06930698328024776</v>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>Ronbay(양극) (CN)</t>
+          <t>Mercedes-Benz (DE)</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.03025861097171367</v>
+        <v>-0.03855444639077721</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>CL (1종목)</t>
+          <t>AU (1종목)</t>
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0</v>
+        <v>0.01408457798608986</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0</v>
+        <v>0.01408457798608986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>NIO (CN)</t>
+          <t>Albemarle (US)</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0</v>
+        <v>0.05930208760557387</v>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
@@ -8720,28 +9618,28 @@
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.03437092933520736</v>
+        <v>-0.04020751507726927</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>DE (3종목)</t>
+          <t>JP (2종목)</t>
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0</v>
+        <v>0.01239417533291814</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0</v>
+        <v>0.01239417533291814</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Xpeng (CN)</t>
+          <t>SQM (CL)</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0</v>
+        <v>0.05845178067412937</v>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
@@ -8749,18 +9647,18 @@
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.04105090209131845</v>
+        <v>-0.04761909236098016</v>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>US (11종목)</t>
+          <t>DE (3종목)</t>
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0</v>
+        <v>-0.02124041486741883</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>0</v>
+        <v>-0.01766540401996675</v>
       </c>
     </row>
     <row r="12">
@@ -8770,7 +9668,7 @@
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0</v>
+        <v>0.05543183714146549</v>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
@@ -8778,7 +9676,7 @@
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.05544892417933134</v>
+        <v>-0.06120428005312961</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
@@ -8786,20 +9684,20 @@
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>-0.02103513276669271</v>
+        <v>-0.02262571464005764</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>-0.01830771640999407</v>
+        <v>-0.02294198107889522</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Tesla (US)</t>
+          <t>Umicore (BE)</t>
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>0</v>
+        <v>0.05379392815106199</v>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
@@ -8807,17 +9705,17 @@
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.06714449910514342</v>
+        <v>-0.0720482772886295</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Lithium Americas (US)</t>
+          <t>Tesla (US)</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>0.04044736360601475</v>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
@@ -8825,7 +9723,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.06743418627581077</v>
+        <v>-0.07264248202946078</v>
       </c>
     </row>
     <row r="15">
@@ -8835,7 +9733,7 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0.007868169994410002</v>
+        <v>0.08263196003527569</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
@@ -8843,7 +9741,7 @@
         </is>
       </c>
       <c r="F15" s="28" t="n">
-        <v>-0.03920139794826623</v>
+        <v>-0.04592820986222514</v>
       </c>
     </row>
     <row r="17">
@@ -8957,13 +9855,13 @@
         </is>
       </c>
       <c r="B19" s="31" t="n">
-        <v>0</v>
+        <v>0.04044736360601475</v>
       </c>
       <c r="C19" s="31" t="n">
-        <v>0.04792487241878374</v>
+        <v>0.09031067076529298</v>
       </c>
       <c r="D19" s="31" t="n">
-        <v>0.03025360451363435</v>
+        <v>0.07192464666180465</v>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
@@ -8985,13 +9883,13 @@
         </is>
       </c>
       <c r="L19" s="31" t="n">
-        <v>-0.02039271214175808</v>
+        <v>-0.02605735040170287</v>
       </c>
       <c r="M19" s="31" t="n">
-        <v>-0.06757725310530349</v>
+        <v>-0.07296904390960679</v>
       </c>
       <c r="N19" s="31" t="n">
-        <v>-0.04912023896113271</v>
+        <v>-0.05461875856357912</v>
       </c>
       <c r="P19" s="29" t="inlineStr">
         <is>
@@ -8999,13 +9897,13 @@
         </is>
       </c>
       <c r="Q19" s="31" t="n">
-        <v>0</v>
+        <v>0.05845178067412937</v>
       </c>
       <c r="R19" s="31" t="n">
-        <v>-0.05129055879248978</v>
+        <v>0.004163197388447504</v>
       </c>
       <c r="S19" s="31" t="n">
-        <v>-0.1753039995564614</v>
+        <v>-0.127099049815704</v>
       </c>
     </row>
     <row r="20">
@@ -9015,13 +9913,13 @@
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>-0.02159242249755078</v>
+        <v>-0.02294198107889522</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>-0.04688868138183644</v>
+        <v>-0.04820334777301583</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>-0.05925608951140615</v>
+        <v>-0.0605536970181757</v>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
@@ -9029,13 +9927,13 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>0</v>
+        <v>-0.01766540401996675</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>-0.003816815111601701</v>
+        <v>-0.01596110650047189</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>-0.007947527482395467</v>
+        <v>-0.02004146209408286</v>
       </c>
       <c r="K20" s="20" t="inlineStr">
         <is>
@@ -9043,13 +9941,13 @@
         </is>
       </c>
       <c r="L20" s="22" t="n">
-        <v>-0.007201867383634708</v>
+        <v>-0.01334457245573584</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>0.06425971747333992</v>
+        <v>0.0576748606431523</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>-0.06316210122954791</v>
+        <v>-0.06895856550909707</v>
       </c>
       <c r="P20" s="20" t="inlineStr">
         <is>
@@ -9057,43 +9955,43 @@
         </is>
       </c>
       <c r="Q20" s="22" t="n">
-        <v>0</v>
+        <v>0.05930208760557387</v>
       </c>
       <c r="R20" s="22" t="n">
-        <v>-0.02453794044579027</v>
+        <v>0.03330899606580706</v>
       </c>
       <c r="S20" s="22" t="n">
-        <v>-0.176698711871518</v>
+        <v>-0.1278752267571409</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>NIO (CN)</t>
+          <t>Xpeng (CN)</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0</v>
+        <v>0.01864035947666287</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>-0.04956270349425007</v>
+        <v>-0.06256305702375853</v>
       </c>
       <c r="D21" s="22" t="n">
-        <v>-0.1117166423180885</v>
+        <v>-0.09718173019506204</v>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>Mercedes-Benz (DE)</t>
+          <t>GM (US)</t>
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>0</v>
+        <v>0.05543183714146549</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>-0.01499030277406699</v>
+        <v>0.0447529477432469</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>-0.03241890223512001</v>
+        <v>-0.03855790685180127</v>
       </c>
       <c r="K21" s="20" t="inlineStr">
         <is>
@@ -9101,57 +9999,57 @@
         </is>
       </c>
       <c r="L21" s="22" t="n">
-        <v>-0.04105090209131845</v>
+        <v>-0.04761909236098016</v>
       </c>
       <c r="M21" s="22" t="n">
-        <v>-0.03630362136045784</v>
+        <v>-0.0429043274781159</v>
       </c>
       <c r="N21" s="22" t="n">
-        <v>-0.1029185948905912</v>
+        <v>-0.1090630308872296</v>
       </c>
       <c r="P21" s="20" t="inlineStr">
         <is>
-          <t>Tianqi (CN)</t>
+          <t>Sigma Lithium (CA)</t>
         </is>
       </c>
       <c r="Q21" s="22" t="n">
-        <v>0.01752921921295592</v>
+        <v>0.07506357070339242</v>
       </c>
       <c r="R21" s="22" t="n">
-        <v>0.02869191459649589</v>
+        <v>-0.001182060146187269</v>
       </c>
       <c r="S21" s="22" t="n">
-        <v>-0.2032680112144618</v>
+        <v>-0.1666667136920258</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Xpeng (CN)</t>
+          <t>NIO (CN)</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>0</v>
+        <v>0.009202445238506662</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>-0.07971745449212364</v>
+        <v>-0.04081635632052161</v>
       </c>
       <c r="D22" s="22" t="n">
-        <v>-0.1137026317426002</v>
+        <v>-0.103542263362744</v>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>Volkswagen (DE)</t>
+          <t>Mercedes-Benz (DE)</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0</v>
+        <v>-0.03855444639077721</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>-0.008039120851968673</v>
+        <v>-0.03832202758904124</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>-0.05212624104553476</v>
+        <v>-0.05533779935136107</v>
       </c>
       <c r="K22" s="20" t="inlineStr">
         <is>
@@ -9169,17 +10067,17 @@
       </c>
       <c r="P22" s="20" t="inlineStr">
         <is>
-          <t>Sigma Lithium (CA)</t>
+          <t>Tianqi (CN)</t>
         </is>
       </c>
       <c r="Q22" s="22" t="n">
-        <v>0</v>
+        <v>0.02170285799804805</v>
       </c>
       <c r="R22" s="22" t="n">
-        <v>-0.07092197422306257</v>
+        <v>0.03291133983913563</v>
       </c>
       <c r="S22" s="22" t="n">
-        <v>-0.2248520840839756</v>
+        <v>-0.2000000249326616</v>
       </c>
     </row>
     <row r="23">
@@ -9189,27 +10087,27 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>-0.01200573540786765</v>
+        <v>-0.01059321988237372</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>-0.05023767143218083</v>
+        <v>-0.04887981533654329</v>
       </c>
       <c r="D23" s="22" t="n">
-        <v>-0.1294337488908417</v>
+        <v>-0.1281891178340305</v>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>GM (US)</t>
+          <t>Volkswagen (DE)</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>0</v>
+        <v>-0.007501394191512523</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>-0.01011802849072774</v>
+        <v>-0.0123456871251838</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>-0.08905335303114303</v>
+        <v>-0.0562414045034777</v>
       </c>
       <c r="K23" s="20" t="inlineStr">
         <is>
@@ -9217,27 +10115,27 @@
         </is>
       </c>
       <c r="L23" s="22" t="n">
-        <v>-0.004431345626716543</v>
+        <v>-0.002954206939861259</v>
       </c>
       <c r="M23" s="22" t="n">
-        <v>-0.04125183926532083</v>
+        <v>-0.03982933164321811</v>
       </c>
       <c r="N23" s="22" t="n">
-        <v>-0.1446700922292609</v>
+        <v>-0.1434010276687783</v>
       </c>
       <c r="P23" s="20" t="inlineStr">
         <is>
-          <t>Ganfeng (CN)</t>
+          <t>Lithium Americas (US)</t>
         </is>
       </c>
       <c r="Q23" s="22" t="n">
-        <v>0.01746723254120064</v>
+        <v>0.06930698328024776</v>
       </c>
       <c r="R23" s="22" t="n">
-        <v>-0.0008576525739882879</v>
+        <v>0.009345785021542818</v>
       </c>
       <c r="S23" s="22" t="n">
-        <v>-0.2952208630007959</v>
+        <v>-0.255172408690209</v>
       </c>
     </row>
     <row r="24">
@@ -9247,13 +10145,13 @@
         </is>
       </c>
       <c r="B24" s="31" t="n">
-        <v>0</v>
+        <v>0.03412068059804296</v>
       </c>
       <c r="C24" s="31" t="n">
-        <v>-0.08045052095321392</v>
+        <v>-0.04907486688456164</v>
       </c>
       <c r="D24" s="31" t="n">
-        <v>-0.2390146500116955</v>
+        <v>-0.2130493119449546</v>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
@@ -9261,13 +10159,13 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>0</v>
+        <v>0.01122626211549349</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>-0.04691355660249552</v>
+        <v>-0.0362139583701917</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>-0.1051004405548026</v>
+        <v>-0.09505406353343127</v>
       </c>
       <c r="K24" s="29" t="inlineStr">
         <is>
@@ -9275,27 +10173,27 @@
         </is>
       </c>
       <c r="L24" s="31" t="n">
-        <v>-0.01793720323835302</v>
+        <v>-0.02298201224774454</v>
       </c>
       <c r="M24" s="31" t="n">
-        <v>-0.1491014951835138</v>
+        <v>-0.1534725195796429</v>
       </c>
       <c r="N24" s="31" t="n">
-        <v>-0.3149560236627872</v>
+        <v>-0.3184750613812011</v>
       </c>
       <c r="P24" s="20" t="inlineStr">
         <is>
-          <t>Lithium Americas (US)</t>
+          <t>Ganfeng (CN)</t>
         </is>
       </c>
       <c r="Q24" s="22" t="n">
-        <v>0</v>
+        <v>0.0218340614990844</v>
       </c>
       <c r="R24" s="22" t="n">
-        <v>-0.05607482153980292</v>
+        <v>0.003430528505701913</v>
       </c>
       <c r="S24" s="22" t="n">
-        <v>-0.3034483053454594</v>
+        <v>-0.2921960481999557</v>
       </c>
     </row>
     <row r="25">
@@ -9305,13 +10203,13 @@
         </is>
       </c>
       <c r="B25" s="28" t="n">
-        <v>-0.005599692984236404</v>
+        <v>0.01147927465965972</v>
       </c>
       <c r="C25" s="28" t="n">
-        <v>-0.04315535988913686</v>
+        <v>-0.02653779542885132</v>
       </c>
       <c r="D25" s="28" t="n">
-        <v>-0.1038116929934996</v>
+        <v>-0.0884319122821937</v>
       </c>
       <c r="F25" s="29" t="inlineStr">
         <is>
@@ -9319,13 +10217,13 @@
         </is>
       </c>
       <c r="G25" s="31" t="n">
-        <v>0</v>
+        <v>0.01470586860331125</v>
       </c>
       <c r="H25" s="31" t="n">
-        <v>-0.05773672157158483</v>
+        <v>-0.04387992160929133</v>
       </c>
       <c r="I25" s="31" t="n">
-        <v>-0.1168831115214801</v>
+        <v>-0.10389611059815</v>
       </c>
       <c r="K25" s="26" t="inlineStr">
         <is>
@@ -9333,13 +10231,13 @@
         </is>
       </c>
       <c r="L25" s="28" t="n">
-        <v>-0.0102355600463212</v>
+        <v>-0.01389276070036185</v>
       </c>
       <c r="M25" s="28" t="n">
-        <v>-0.04653778054878763</v>
+        <v>-0.05012542563648353</v>
       </c>
       <c r="N25" s="28" t="n">
-        <v>-0.1357975105949235</v>
+        <v>-0.1390790761010177</v>
       </c>
       <c r="P25" s="29" t="inlineStr">
         <is>
@@ -9363,13 +10261,13 @@
         </is>
       </c>
       <c r="G26" s="28" t="n">
-        <v>-0.0006874742197167581</v>
+        <v>0.001832914817142349</v>
       </c>
       <c r="H26" s="28" t="n">
-        <v>-0.02023064934320649</v>
+        <v>-0.01456710763584758</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>-0.05401071863084723</v>
+        <v>-0.04909631449682268</v>
       </c>
       <c r="P26" s="26" t="inlineStr">
         <is>
@@ -9377,13 +10275,13 @@
         </is>
       </c>
       <c r="Q26" s="28" t="n">
-        <v>0.00701157567717806</v>
+        <v>0.04567798853522368</v>
       </c>
       <c r="R26" s="28" t="n">
-        <v>-0.02743655181884413</v>
+        <v>0.009273279560168102</v>
       </c>
       <c r="S26" s="28" t="n">
-        <v>-0.2413995291554673</v>
+        <v>-0.2114306001576138</v>
       </c>
     </row>
     <row r="27">
@@ -9452,13 +10350,13 @@
         </is>
       </c>
       <c r="B29" s="31" t="n">
-        <v>-0.01061832884645075</v>
+        <v>-0.01270040861659361</v>
       </c>
       <c r="C29" s="31" t="n">
-        <v>0.02083783537274186</v>
+        <v>0.01868955845636444</v>
       </c>
       <c r="D29" s="31" t="n">
-        <v>0.0004210622687088605</v>
+        <v>-0.001684249074835553</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -9486,13 +10384,13 @@
         </is>
       </c>
       <c r="L29" s="22" t="n">
-        <v>-0.03437092933520736</v>
+        <v>-0.04020751507726927</v>
       </c>
       <c r="M29" s="22" t="n">
-        <v>-0.02552352071099173</v>
+        <v>-0.03141358315606413</v>
       </c>
       <c r="N29" s="22" t="n">
-        <v>-0.08114776837854887</v>
+        <v>-0.0867016192277692</v>
       </c>
     </row>
     <row r="30">
@@ -9502,13 +10400,13 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>-0.01830771640999407</v>
+        <v>-0.02226614923186976</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>0.009669238562144411</v>
+        <v>0.005597995546413603</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>-0.09981854226646314</v>
+        <v>-0.1034483027194083</v>
       </c>
       <c r="F30" s="29" t="inlineStr">
         <is>
@@ -9516,13 +10414,13 @@
         </is>
       </c>
       <c r="G30" s="31" t="n">
-        <v>0</v>
+        <v>0.2499999332783844</v>
       </c>
       <c r="H30" s="31" t="n">
-        <v>0.1911111407809787</v>
+        <v>0.4888888465033636</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>-0.08843536918467498</v>
+        <v>0.1394557276980914</v>
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
@@ -9530,13 +10428,13 @@
         </is>
       </c>
       <c r="L30" s="22" t="n">
-        <v>-0.05544892417933134</v>
+        <v>-0.06120428005312961</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>0.004144768965871792</v>
+        <v>-0.001973704287880351</v>
       </c>
       <c r="N30" s="22" t="n">
-        <v>-0.1073224429948386</v>
+        <v>-0.1127617221959699</v>
       </c>
     </row>
     <row r="31">
@@ -9546,13 +10444,13 @@
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>-0.06743418627581077</v>
+        <v>-0.07264248202946078</v>
       </c>
       <c r="C31" s="22" t="n">
-        <v>-0.07729857761553793</v>
+        <v>-0.08245178163542399</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>-0.1096571244989029</v>
+        <v>-0.1146296089600761</v>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
@@ -9560,13 +10458,13 @@
         </is>
       </c>
       <c r="G31" s="22" t="n">
+        <v>0.01507536243517626</v>
+      </c>
+      <c r="H31" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="22" t="n">
-        <v>-0.0148514711252673</v>
-      </c>
       <c r="I31" s="22" t="n">
-        <v>-0.1531914509384257</v>
+        <v>-0.1404255051481168</v>
       </c>
       <c r="K31" s="26" t="inlineStr">
         <is>
@@ -9574,13 +10472,13 @@
         </is>
       </c>
       <c r="L31" s="28" t="n">
-        <v>-0.04490992675726935</v>
+        <v>-0.05070589756519944</v>
       </c>
       <c r="M31" s="28" t="n">
-        <v>-0.01068937587255997</v>
+        <v>-0.01669364372197224</v>
       </c>
       <c r="N31" s="28" t="n">
-        <v>-0.09423510568669374</v>
+        <v>-0.09973167071186956</v>
       </c>
     </row>
     <row r="32">
@@ -9590,13 +10488,13 @@
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>-0.01421806345902454</v>
+        <v>-0.01800952896896424</v>
       </c>
       <c r="C32" s="22" t="n">
-        <v>-0.01515159040990199</v>
+        <v>-0.01893946543486147</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>-0.1275168161103113</v>
+        <v>-0.1308725175865704</v>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
@@ -9604,29 +10502,29 @@
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>0</v>
+        <v>0.07179480157033469</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>-0.02010048324690161</v>
+        <v>0.05025120811725392</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>-0.2057026035503878</v>
+        <v>-0.1486761795844543</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>Ronbay(양극) (CN)</t>
+          <t>Umicore (BE)</t>
         </is>
       </c>
       <c r="B33" s="22" t="n">
-        <v>-0.03025861097171367</v>
+        <v>0.05379392815106199</v>
       </c>
       <c r="C33" s="22" t="n">
-        <v>-0.04791566649676915</v>
+        <v>0.00161467635999446</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>-0.1668762884099823</v>
+        <v>-0.1336126160636764</v>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
@@ -9634,29 +10532,29 @@
         </is>
       </c>
       <c r="G33" s="31" t="n">
-        <v>0</v>
+        <v>0.09272731434215209</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>-0.07251262070594255</v>
+        <v>0.01349079306223633</v>
       </c>
       <c r="I33" s="31" t="n">
-        <v>-0.2744063251506064</v>
+        <v>-0.2071239723781694</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>Xiamen Tungsten NE(양극) (CN)</t>
+          <t>Ronbay(양극) (CN)</t>
         </is>
       </c>
       <c r="B34" s="22" t="n">
-        <v>-0.02989497921950657</v>
+        <v>-0.03513905912138526</v>
       </c>
       <c r="C34" s="22" t="n">
-        <v>-0.05210525111148234</v>
+        <v>-0.05270725142482224</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>-0.1687053095864843</v>
+        <v>-0.1710691764548571</v>
       </c>
       <c r="F34" s="26" t="inlineStr">
         <is>
@@ -9664,45 +10562,45 @@
         </is>
       </c>
       <c r="G34" s="28" t="n">
-        <v>0</v>
+        <v>0.1073993529065119</v>
       </c>
       <c r="H34" s="28" t="n">
-        <v>0.0209116414257168</v>
+        <v>0.1381577119207135</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>-0.1804339372060237</v>
+        <v>-0.08919248235316227</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>Tinci(전해액) (CN)</t>
+          <t>Xiamen Tungsten NE(양극) (CN)</t>
         </is>
       </c>
       <c r="B35" s="22" t="n">
-        <v>-0.02442581366532182</v>
+        <v>-0.03555075833158938</v>
       </c>
       <c r="C35" s="22" t="n">
-        <v>-0.04734780763550561</v>
+        <v>-0.05763154280813121</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>-0.1851400698981706</v>
+        <v>-0.1735518149083962</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>Umicore (BE)</t>
+          <t>Tinci(전해액) (CN)</t>
         </is>
       </c>
       <c r="B36" s="22" t="n">
-        <v>0</v>
+        <v>-0.03025883756732739</v>
       </c>
       <c r="C36" s="22" t="n">
-        <v>-0.07319701915694576</v>
+        <v>-0.05304377938854843</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>-0.1983240372284626</v>
+        <v>-0.1900121724154874</v>
       </c>
     </row>
     <row r="37">
@@ -9712,13 +10610,13 @@
         </is>
       </c>
       <c r="B37" s="31" t="n">
-        <v>-0.06714449910514342</v>
+        <v>-0.0720482772886295</v>
       </c>
       <c r="C37" s="31" t="n">
-        <v>-0.1134612247208789</v>
+        <v>-0.1181215279520417</v>
       </c>
       <c r="D37" s="31" t="n">
-        <v>-0.3165676771124815</v>
+        <v>-0.3201603026709416</v>
       </c>
     </row>
     <row r="38">
@@ -9728,13 +10626,13 @@
         </is>
       </c>
       <c r="B38" s="28" t="n">
-        <v>-0.02914468866144062</v>
+        <v>-0.02720239700052866</v>
       </c>
       <c r="C38" s="28" t="n">
-        <v>-0.04399667369023727</v>
+        <v>-0.0396659020312285</v>
       </c>
       <c r="D38" s="28" t="n">
-        <v>-0.1524649780936166</v>
+        <v>-0.1487823067615832</v>
       </c>
     </row>
   </sheetData>
@@ -11027,10 +11925,10 @@
         <v>-0.004251609381155023</v>
       </c>
       <c r="U17" s="22" t="n">
-        <v>-0.005599692984236404</v>
+        <v>0.01147927465965972</v>
       </c>
       <c r="V17" s="22" t="n">
-        <v>-0.1038116929934996</v>
+        <v>-0.0884319122821937</v>
       </c>
     </row>
     <row r="18">
@@ -11094,13 +11992,13 @@
         <v>-0.01591714674896998</v>
       </c>
       <c r="T18" s="22" t="n">
-        <v>0.001743377013509382</v>
+        <v>0.005203475756635585</v>
       </c>
       <c r="U18" s="22" t="n">
-        <v>-0.0006874742197167581</v>
+        <v>0.001832914817142349</v>
       </c>
       <c r="V18" s="22" t="n">
-        <v>-0.05401071863084723</v>
+        <v>-0.04909631449682268</v>
       </c>
     </row>
     <row r="19">
@@ -11167,10 +12065,10 @@
         <v>0.005396120096030669</v>
       </c>
       <c r="U19" s="22" t="n">
-        <v>-0.0102355600463212</v>
+        <v>-0.01389276070036185</v>
       </c>
       <c r="V19" s="22" t="n">
-        <v>-0.1357975105949235</v>
+        <v>-0.1390790761010177</v>
       </c>
     </row>
     <row r="20">
@@ -11237,10 +12135,10 @@
         <v>0.01424052490168895</v>
       </c>
       <c r="U20" s="22" t="n">
-        <v>0.00701157567717806</v>
+        <v>0.04567798853522368</v>
       </c>
       <c r="V20" s="22" t="n">
-        <v>-0.2413995291554674</v>
+        <v>-0.2114306001576138</v>
       </c>
     </row>
     <row r="21">
@@ -11304,13 +12202,13 @@
         <v>0.04065104712189489</v>
       </c>
       <c r="T21" s="22" t="n">
-        <v>0.003112811499904821</v>
+        <v>0.005951891068898152</v>
       </c>
       <c r="U21" s="22" t="n">
-        <v>-0.02914468866144062</v>
+        <v>-0.02720239700052866</v>
       </c>
       <c r="V21" s="22" t="n">
-        <v>-0.1524649780936166</v>
+        <v>-0.1487823067615832</v>
       </c>
     </row>
     <row r="22">
@@ -11377,10 +12275,10 @@
         <v>0.02651829625667401</v>
       </c>
       <c r="U22" s="22" t="n">
-        <v>-0.04490992675726935</v>
+        <v>-0.05070589756519944</v>
       </c>
       <c r="V22" s="22" t="n">
-        <v>-0.09423510568669374</v>
+        <v>-0.09973167071186956</v>
       </c>
     </row>
     <row r="23">
@@ -11447,10 +12345,10 @@
         <v>-0.02068357075828217</v>
       </c>
       <c r="U23" s="22" t="n">
-        <v>0</v>
+        <v>0.1073993529065119</v>
       </c>
       <c r="V23" s="22" t="n">
-        <v>-0.1804339372060237</v>
+        <v>-0.08919248235316227</v>
       </c>
     </row>
   </sheetData>
@@ -12136,22 +13034,22 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>4.986000061035156</v>
+        <v>4.993000030517578</v>
       </c>
       <c r="M5" s="21" t="n">
-        <v>0</v>
+        <v>0.006999969482421875</v>
       </c>
       <c r="N5" s="21" t="n">
-        <v>-0.1310000419616699</v>
+        <v>-0.124000072479248</v>
       </c>
       <c r="O5" s="21" t="n">
-        <v>-0.1979999542236328</v>
+        <v>-0.1909999847412109</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>0.3450002670288086</v>
+        <v>0.3520002365112305</v>
       </c>
       <c r="Q5" s="21" t="n">
-        <v>0.8229999542236328</v>
+        <v>0.8299999237060547</v>
       </c>
     </row>
     <row r="6">
@@ -12194,22 +13092,22 @@
         </is>
       </c>
       <c r="L6" s="21" t="n">
-        <v>1323.969970703125</v>
+        <v>1326.81005859375</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>2.2099609375</v>
+        <v>5.050048828125</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>-6.030029296875</v>
+        <v>-3.18994140625</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>-43.3900146484375</v>
+        <v>-40.5499267578125</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>-134.0400390625</v>
+        <v>-131.199951171875</v>
       </c>
       <c r="Q6" s="21" t="n">
-        <v>-113.9400634765625</v>
+        <v>-111.0999755859375</v>
       </c>
     </row>
     <row r="7">
@@ -12284,22 +13182,22 @@
         </is>
       </c>
       <c r="C9" s="21" t="n">
-        <v>26169.380859375</v>
+        <v>26477.810546875</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>0</v>
+        <v>0.0117858992980151</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>-0.009666648632012387</v>
+        <v>0.002005320518676745</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.03322432018910204</v>
+        <v>-0.02182999938308061</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>0.04962685734093997</v>
+        <v>0.06199765378205235</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>0.1259526656486749</v>
+        <v>0.1392230303803419</v>
       </c>
     </row>
     <row r="10">
@@ -12314,22 +13212,22 @@
         </is>
       </c>
       <c r="C10" s="21" t="n">
-        <v>7019.18994140625</v>
+        <v>7150.7724609375</v>
       </c>
       <c r="D10" s="22" t="n">
-        <v>0</v>
+        <v>0.01874611182054564</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.01250130003628425</v>
+        <v>0.006010461015878876</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.009203360353428836</v>
+        <v>0.00937022424480638</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.07774975062330114</v>
+        <v>0.09795336796305065</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0.2298832529427175</v>
+        <v>0.252938781928598</v>
       </c>
     </row>
     <row r="11">
@@ -12344,22 +13242,22 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>7676.77001953125</v>
+        <v>7722.60009765625</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>0.005969968881235133</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-0.004641747887336178</v>
+        <v>0.001300509903457092</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.008606045059483591</v>
+        <v>-0.002687453999444034</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0.03555691855583709</v>
+        <v>0.04173916113436316</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.1214330610665766</v>
+        <v>0.1281279815435323</v>
       </c>
     </row>
     <row r="12">
@@ -12374,22 +13272,22 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>179.2799987792969</v>
+        <v>179.1799926757812</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0</v>
+        <v>-0.0005578207507617172</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.003003050399993712</v>
+        <v>-0.003559195986926778</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.05026363201199247</v>
+        <v>0.0496777731642859</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.09718485603416016</v>
+        <v>0.09657282355404284</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0.1581395041662506</v>
+        <v>0.1574934699185497</v>
       </c>
     </row>
     <row r="13">
@@ -12404,22 +13302,22 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>48.72000122070312</v>
+        <v>51.65000152587891</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>0</v>
+        <v>0.06013957782765211</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0.00143884260285132</v>
+        <v>0.06166495181719944</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.08695650930611687</v>
+        <v>-0.03204645923750093</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.2892299560830338</v>
+        <v>0.3667637013646299</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.6817398127532694</v>
+        <v>0.7828789351082057</v>
       </c>
     </row>
     <row r="14">
@@ -12434,22 +13332,22 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>150.4700012207031</v>
+        <v>154.8399963378906</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0</v>
+        <v>0.02904230133405639</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.01807624754088455</v>
+        <v>0.01044107796510052</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.02941364635553811</v>
+        <v>-0.001225585002272656</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.0007968332565614356</v>
+        <v>0.02822232620594489</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0.2340687348814503</v>
+        <v>0.2699089309468152</v>
       </c>
     </row>
     <row r="15">
@@ -12464,22 +13362,22 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>73.48999786376953</v>
+        <v>73.91000366210938</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>0</v>
+        <v>0.005715142339756563</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.007026135082441431</v>
+        <v>-0.001351148104779543</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.02377790840267147</v>
+        <v>-0.01819866019397798</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>-0.02377790840267147</v>
+        <v>-0.01819866019397798</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>0.03536199476089141</v>
+        <v>0.04127923593412408</v>
       </c>
     </row>
     <row r="16">
@@ -12494,22 +13392,22 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>118.9400024414062</v>
+        <v>120.2799987792969</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>0</v>
+        <v>0.004677560582056817</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>0.02340389943326371</v>
+        <v>0.03493372496945479</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>0.07618536060522119</v>
+        <v>0.08830983019074101</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.02446170546607029</v>
+        <v>0.03600344840751668</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>0.04296739290197382</v>
+        <v>0.05471762376073341</v>
       </c>
     </row>
     <row r="17">
@@ -12584,22 +13482,22 @@
         </is>
       </c>
       <c r="C19" s="21" t="n">
-        <v>23049.8203125</v>
+        <v>23211.810546875</v>
       </c>
       <c r="D19" s="22" t="n">
-        <v>-0.00697878496155524</v>
+        <v>0</v>
       </c>
       <c r="E19" s="22" t="n">
-        <v>-0.03426884631067872</v>
+        <v>-0.02748185127954894</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>-0.05957830185687241</v>
+        <v>-0.05296917739393991</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>-0.08558511510392475</v>
+        <v>-0.07915876212103512</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>-0.1006892107773045</v>
+        <v>-0.09436900682139138</v>
       </c>
     </row>
     <row r="20">
@@ -12614,22 +13512,22 @@
         </is>
       </c>
       <c r="C20" s="21" t="n">
-        <v>66.81999969482422</v>
+        <v>68.83999633789062</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>-0.03131347574647891</v>
+        <v>0</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.05514707944797359</v>
+        <v>-0.02658377899266962</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.1057280700858715</v>
+        <v>-0.07869385421240183</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>-0.03467208153069323</v>
+        <v>-0.00548981329256093</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>0.09268351776923778</v>
+        <v>0.1257157992404814</v>
       </c>
     </row>
     <row r="22">
@@ -13108,22 +14006,22 @@
         </is>
       </c>
       <c r="J33" s="22" t="n">
-        <v>0</v>
+        <v>0.0117858992980151</v>
       </c>
       <c r="K33" s="22" t="n">
-        <v>0</v>
+        <v>0.01874611182054564</v>
       </c>
       <c r="L33" s="22" t="n">
-        <v>0</v>
+        <v>0.005969968881235133</v>
       </c>
       <c r="M33" s="22" t="n">
-        <v>0</v>
+        <v>-0.0005578207507617172</v>
       </c>
       <c r="N33" s="22" t="n">
-        <v>0</v>
+        <v>0.06013957782765211</v>
       </c>
       <c r="O33" s="22" t="n">
-        <v>0</v>
+        <v>0.02904230133405639</v>
       </c>
     </row>
     <row r="35">
@@ -13372,7 +14270,7 @@
         <v>0.002592016427032995</v>
       </c>
       <c r="C45" s="22" t="n">
-        <v>0</v>
+        <v>0.006557917969449489</v>
       </c>
       <c r="I45" s="20" t="inlineStr">
         <is>
@@ -13393,10 +14291,10 @@
         </is>
       </c>
       <c r="B46" s="22" t="n">
-        <v>0</v>
+        <v>0.005715142339756563</v>
       </c>
       <c r="C46" s="22" t="n">
-        <v>0</v>
+        <v>0.004677560582056817</v>
       </c>
       <c r="I46" s="20" t="inlineStr">
         <is>
@@ -13656,7 +14554,7 @@
         <v>0.005128805828580552</v>
       </c>
       <c r="C58" s="22" t="n">
-        <v>0</v>
+        <v>-0.002029675445483936</v>
       </c>
       <c r="I58" s="20" t="inlineStr">
         <is>
@@ -13677,10 +14575,10 @@
         </is>
       </c>
       <c r="B59" s="22" t="n">
-        <v>-0.00697878496155524</v>
+        <v>0</v>
       </c>
       <c r="C59" s="22" t="n">
-        <v>-0.03131347574647891</v>
+        <v>0</v>
       </c>
       <c r="I59" s="20" t="inlineStr">
         <is>
@@ -13688,10 +14586,10 @@
         </is>
       </c>
       <c r="J59" s="21" t="n">
-        <v>4.986000061035156</v>
+        <v>4.993000030517578</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>1323.969970703125</v>
+        <v>1326.81005859375</v>
       </c>
     </row>
     <row r="61">
@@ -17607,341 +18505,341 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
+          <t>Moderna</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="n">
+        <v>0.04586369040612404</v>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
           <t>Abbott Laboratories</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific</t>
-        </is>
-      </c>
       <c r="E5" s="22" t="n">
-        <v>0</v>
+        <v>-0.01697176607466844</v>
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>Moderna Inc</t>
+          <t>Prime Medicine Inc</t>
         </is>
       </c>
       <c r="H5" s="22" t="n">
-        <v>0</v>
+        <v>0.2049861581830046</v>
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>Vanda Pharmaceuticals Inc</t>
+          <t>Abbvie Inc</t>
         </is>
       </c>
       <c r="K5" s="22" t="n">
-        <v>0</v>
+        <v>-0.001220532879461445</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Illumina, Inc.</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>0</v>
+        <v>0.03110239230376965</v>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0</v>
+        <v>-0.02023533622385298</v>
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>Natera Inc</t>
+          <t>Neurogene Inc</t>
         </is>
       </c>
       <c r="H6" s="22" t="n">
-        <v>0</v>
+        <v>0.1465589941126615</v>
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>Neurogene Inc</t>
+          <t>Immix Biopharma Inc</t>
         </is>
       </c>
       <c r="K6" s="22" t="n">
-        <v>0</v>
+        <v>-0.001240723121737952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Agilent Technologies</t>
+          <t>Incyte</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>0</v>
+        <v>0.02903539834449331</v>
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>Universal Health Services</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="E7" s="22" t="n">
-        <v>0</v>
+        <v>-0.02060841239960054</v>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>Twist Bioscience Corp</t>
+          <t>Faeth Therapeutics Inc</t>
         </is>
       </c>
       <c r="H7" s="22" t="n">
-        <v>0</v>
+        <v>0.1354724121795148</v>
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>Ovid Therapeutics Inc</t>
+          <t>Alkermes Plc</t>
         </is>
       </c>
       <c r="K7" s="22" t="n">
-        <v>0</v>
+        <v>-0.00270024607544983</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Align Technology</t>
+          <t>Waters Corporation</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>0</v>
+        <v>0.02756694702351226</v>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="E8" s="22" t="n">
-        <v>0</v>
+        <v>-0.02279054280562187</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Halozyme Therapeutics Inc</t>
+          <t>Uniqure Nv</t>
         </is>
       </c>
       <c r="H8" s="22" t="n">
-        <v>0</v>
+        <v>0.1214781115221919</v>
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>Assembly Biosciences Inc</t>
+          <t>United Therapeutics Corp</t>
         </is>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0</v>
+        <v>-0.002766369634547794</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Viatris</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0</v>
+        <v>0.02351002604172092</v>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>Vertex Pharmaceuticals</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>0</v>
+        <v>-0.02452743812525582</v>
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>Abbvie Inc</t>
+          <t>Absci Corp</t>
         </is>
       </c>
       <c r="H9" s="22" t="n">
-        <v>0</v>
+        <v>0.1185185088004967</v>
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>Aura Biosciences Inc</t>
+          <t>Avalo Therapeutics Inc</t>
         </is>
       </c>
       <c r="K9" s="22" t="n">
-        <v>0</v>
+        <v>-0.002954206939861259</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Baxter International</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0</v>
+        <v>0.01187052622892404</v>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Viatris</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>0</v>
+        <v>-0.02603560960958085</v>
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>Iovance Biotherapeutics Inc</t>
+          <t>Immunitybio Inc</t>
         </is>
       </c>
       <c r="H10" s="22" t="n">
-        <v>0</v>
+        <v>0.1049936207002766</v>
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>Faeth Therapeutics Inc</t>
+          <t>Alnylam Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0</v>
+        <v>-0.003821533699295832</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Becton Dickinson</t>
+          <t>Regeneron Pharmaceuticals</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0</v>
+        <v>0.01043742228156952</v>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>Waters Corporation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="E11" s="22" t="n">
-        <v>0</v>
+        <v>-0.03288487725015155</v>
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>Biogen Inc</t>
+          <t>Twist Bioscience Corp</t>
         </is>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0</v>
+        <v>0.1005163931395223</v>
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>Lexeo Therapeutics Inc</t>
+          <t>Arcutis Biotherapeutics Inc</t>
         </is>
       </c>
       <c r="K11" s="22" t="n">
-        <v>0</v>
+        <v>-0.004086738854107375</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Bio-Techne</t>
+          <t>Centene Corporation</t>
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0</v>
+        <v>0.009995594846059497</v>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services</t>
+          <t>Solventum</t>
         </is>
       </c>
       <c r="E12" s="22" t="n">
-        <v>0</v>
+        <v>-0.03297977254605733</v>
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Amgen Inc</t>
+          <t>Intellia Therapeutics Inc</t>
         </is>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0</v>
+        <v>0.09058609976517262</v>
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>Compass Therapeutics Inc</t>
+          <t>Altimmune Inc</t>
         </is>
       </c>
       <c r="K12" s="22" t="n">
-        <v>0</v>
+        <v>-0.004878044241882984</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Biogen</t>
+          <t>Mettler Toledo</t>
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>0</v>
+        <v>0.009403308068775873</v>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>Zimmer Biomet</t>
+          <t>Zoetis</t>
         </is>
       </c>
       <c r="E13" s="22" t="n">
-        <v>0</v>
+        <v>-0.03383966682056738</v>
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>Gilead Sciences Inc</t>
+          <t>Sagimet Biosciences Inc A</t>
         </is>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0</v>
+        <v>0.08995811913486573</v>
       </c>
       <c r="J13" s="20" t="inlineStr">
         <is>
-          <t>Crescent Biopharma Inc</t>
+          <t>Biomarin Pharmaceutical Inc</t>
         </is>
       </c>
       <c r="K13" s="22" t="n">
-        <v>0</v>
+        <v>-0.007174915262401882</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Boston Scientific</t>
+          <t>Revvity</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>0.009165167568408794</v>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Zoetis</t>
+          <t>Universal Health Services</t>
         </is>
       </c>
       <c r="E14" s="22" t="n">
-        <v>0</v>
+        <v>-0.04517796072548386</v>
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>Exelixis Inc</t>
+          <t>Climb Bio Inc</t>
         </is>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0</v>
+        <v>0.08626552088638673</v>
       </c>
       <c r="J14" s="20" t="inlineStr">
         <is>
-          <t>Bridgebio Oncology Therapeut</t>
+          <t>Ars Pharmaceuticals Inc</t>
         </is>
       </c>
       <c r="K14" s="22" t="n">
-        <v>0</v>
+        <v>-0.04846940140881051</v>
       </c>
     </row>
     <row r="15">
@@ -17951,7 +18849,7 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0</v>
+        <v>0.02079504731133579</v>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
@@ -17959,7 +18857,7 @@
         </is>
       </c>
       <c r="E15" s="28" t="n">
-        <v>0</v>
+        <v>-0.02760513825808406</v>
       </c>
       <c r="G15" s="26" t="inlineStr">
         <is>
@@ -17967,7 +18865,7 @@
         </is>
       </c>
       <c r="H15" s="28" t="n">
-        <v>0</v>
+        <v>0.1199333938424093</v>
       </c>
       <c r="J15" s="26" t="inlineStr">
         <is>
@@ -17975,7 +18873,7 @@
         </is>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0</v>
+        <v>-0.007931271211755686</v>
       </c>
     </row>
     <row r="17">
@@ -18015,173 +18913,173 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>Genscript</t>
+          <t>프라임</t>
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>0.04668768159673364</v>
+        <v>0.2049861581830046</v>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>HCA</t>
+          <t>Insilico</t>
         </is>
       </c>
       <c r="E19" s="22" t="n">
-        <v>0</v>
+        <v>-0.01666674945089219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>Biocon</t>
+          <t>Absci</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>0.01216545057330909</v>
+        <v>0.1185185088004967</v>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>유나이티드</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>0</v>
+        <v>-0.01697176607466844</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Twist</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0</v>
+        <v>0.1005163931395223</v>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>일루미나</t>
+          <t>Elevance</t>
         </is>
       </c>
       <c r="E21" s="22" t="n">
-        <v>0</v>
+        <v>-0.02279054280562187</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>슈뢰딩거</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>0</v>
+        <v>0.09061221687161192</v>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>Cigna</t>
         </is>
       </c>
       <c r="E22" s="22" t="n">
-        <v>-0.00736842105263158</v>
+        <v>-0.02452743812525582</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>Pfizer</t>
+          <t>인텔리아</t>
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>0</v>
+        <v>0.09058609976517262</v>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>Tenet</t>
         </is>
       </c>
       <c r="E23" s="22" t="n">
-        <v>-0.007782101167315147</v>
+        <v>-0.02565541587985143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>에디타스</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>0</v>
+        <v>0.08333325054910778</v>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>우시 XDC</t>
+          <t>우시 바이오</t>
         </is>
       </c>
       <c r="E24" s="22" t="n">
-        <v>-0.01490412303544431</v>
+        <v>-0.02701528621448235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="20" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Dyne</t>
         </is>
       </c>
       <c r="B25" s="22" t="n">
-        <v>0</v>
+        <v>0.07760815816190814</v>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>Insilico</t>
+          <t>HCA</t>
         </is>
       </c>
       <c r="E25" s="22" t="n">
-        <v>-0.01666674945089219</v>
+        <v>-0.03288487725015155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Wave Life</t>
         </is>
       </c>
       <c r="B26" s="22" t="n">
-        <v>0</v>
+        <v>0.07476635722262714</v>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>우시 바이오</t>
+          <t>Akeso</t>
         </is>
       </c>
       <c r="E26" s="22" t="n">
-        <v>-0.02483667029298375</v>
+        <v>-0.03864447156916506</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Tempus AI</t>
         </is>
       </c>
       <c r="B27" s="22" t="n">
-        <v>0</v>
+        <v>0.07430014281825903</v>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Akeso</t>
+          <t>메타비아</t>
         </is>
       </c>
       <c r="E27" s="22" t="n">
-        <v>-0.03448277738995775</v>
+        <v>-0.05349798801215722</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="B28" s="22" t="n">
-        <v>0</v>
+        <v>0.06877830006908736</v>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
@@ -18199,7 +19097,7 @@
         </is>
       </c>
       <c r="B29" s="28" t="n">
-        <v>0.005885313217004274</v>
+        <v>0.09840055855807976</v>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
@@ -18207,7 +19105,7 @@
         </is>
       </c>
       <c r="E29" s="28" t="n">
-        <v>-0.01597598506536876</v>
+        <v>-0.03123735436467088</v>
       </c>
     </row>
     <row r="31">
@@ -18321,13 +19219,13 @@
         </is>
       </c>
       <c r="B33" s="31" t="n">
-        <v>0</v>
+        <v>0.002165532701290163</v>
       </c>
       <c r="C33" s="31" t="n">
-        <v>-0.003521196742826471</v>
+        <v>-0.001363289308230486</v>
       </c>
       <c r="D33" s="31" t="n">
-        <v>0.1113389564647451</v>
+        <v>0.1137455973171873</v>
       </c>
       <c r="F33" s="29" t="inlineStr">
         <is>
@@ -18335,13 +19233,13 @@
         </is>
       </c>
       <c r="G33" s="31" t="n">
-        <v>0</v>
+        <v>0.00157529933716094</v>
       </c>
       <c r="H33" s="31" t="n">
-        <v>0.01087998046875005</v>
+        <v>0.01727998046875001</v>
       </c>
       <c r="I33" s="31" t="n">
-        <v>0.1245995043093451</v>
+        <v>0.1317194759841647</v>
       </c>
       <c r="K33" s="29" t="inlineStr">
         <is>
@@ -18349,13 +19247,13 @@
         </is>
       </c>
       <c r="L33" s="31" t="n">
-        <v>0</v>
+        <v>-0.00315689818241438</v>
       </c>
       <c r="M33" s="31" t="n">
-        <v>0.06794602797134575</v>
+        <v>0.06457463109672634</v>
       </c>
       <c r="N33" s="31" t="n">
-        <v>0.1535013844572568</v>
+        <v>0.1498598980332511</v>
       </c>
       <c r="P33" s="29" t="inlineStr">
         <is>
@@ -18363,13 +19261,13 @@
         </is>
       </c>
       <c r="Q33" s="31" t="n">
-        <v>0</v>
+        <v>-0.003813169876648925</v>
       </c>
       <c r="R33" s="31" t="n">
-        <v>0.06849877497048418</v>
+        <v>0.07157509841269949</v>
       </c>
       <c r="S33" s="31" t="n">
-        <v>0.1857077856723475</v>
+        <v>0.1891215665227575</v>
       </c>
     </row>
     <row r="34">
@@ -18379,13 +19277,13 @@
         </is>
       </c>
       <c r="B34" s="22" t="n">
-        <v>0</v>
+        <v>0.00746689896713959</v>
       </c>
       <c r="C34" s="22" t="n">
-        <v>0.01296305283127119</v>
+        <v>0.02052674560420753</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>0.09490509220240506</v>
+        <v>0.1030806379044871</v>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
@@ -18393,13 +19291,13 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0</v>
+        <v>-0.004163631435895487</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>0.03893148195541407</v>
+        <v>0.03460575417740297</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>0.05149848252319056</v>
+        <v>0.04712043038656066</v>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
@@ -18407,13 +19305,13 @@
         </is>
       </c>
       <c r="L34" s="22" t="n">
-        <v>0</v>
+        <v>0.02351002604172092</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>-0.0193028799124072</v>
+        <v>0.003753334919892826</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>0.06834112260162351</v>
+        <v>0.09345785021542907</v>
       </c>
       <c r="P34" s="20" t="inlineStr">
         <is>
@@ -18421,29 +19319,29 @@
         </is>
       </c>
       <c r="Q34" s="22" t="n">
-        <v>0</v>
+        <v>0.009489426108681975</v>
       </c>
       <c r="R34" s="22" t="n">
-        <v>-0.01469278437923871</v>
+        <v>-0.005342784362254216</v>
       </c>
       <c r="S34" s="22" t="n">
-        <v>0.1407216286555344</v>
+        <v>0.1515464222612366</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>Roche</t>
+          <t>Novartis</t>
         </is>
       </c>
       <c r="B35" s="22" t="n">
-        <v>0</v>
+        <v>0.01982968012593544</v>
       </c>
       <c r="C35" s="22" t="n">
-        <v>0.01471830355103076</v>
+        <v>0.02095809186081055</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>0.08935702953563585</v>
+        <v>0.09915207925716829</v>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
@@ -18451,13 +19349,13 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>0</v>
+        <v>0.01187052622892404</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-0.003607926569921371</v>
+        <v>0.00821977167202248</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>0.02944540390036021</v>
+        <v>0.04166546256860482</v>
       </c>
       <c r="K35" s="20" t="inlineStr">
         <is>
@@ -18479,29 +19377,29 @@
         </is>
       </c>
       <c r="Q35" s="22" t="n">
-        <v>0</v>
+        <v>0.003827869027350772</v>
       </c>
       <c r="R35" s="22" t="n">
-        <v>0.02926744134331805</v>
+        <v>0.0332073423028969</v>
       </c>
       <c r="S35" s="22" t="n">
-        <v>0.1384737791476249</v>
+        <v>0.142831707665275</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="20" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Roche</t>
         </is>
       </c>
       <c r="B36" s="22" t="n">
-        <v>0</v>
+        <v>0.005501864514392052</v>
       </c>
       <c r="C36" s="22" t="n">
-        <v>-0.008094632788789302</v>
+        <v>0.02030114617744228</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>0.08171119948432803</v>
+        <v>0.09535052431994151</v>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
@@ -18523,13 +19421,13 @@
         </is>
       </c>
       <c r="L36" s="22" t="n">
-        <v>0.01216545057330909</v>
+        <v>0</v>
       </c>
       <c r="M36" s="22" t="n">
-        <v>-0.02117650649126834</v>
+        <v>-0.03294121237362135</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>-0.1574683853342563</v>
+        <v>-0.1675949676127373</v>
       </c>
       <c r="P36" s="20" t="inlineStr">
         <is>
@@ -18537,71 +19435,71 @@
         </is>
       </c>
       <c r="Q36" s="22" t="n">
-        <v>0</v>
+        <v>0.006709473321167891</v>
       </c>
       <c r="R36" s="22" t="n">
-        <v>-0.01378549748247859</v>
+        <v>-0.007168517588888368</v>
       </c>
       <c r="S36" s="22" t="n">
-        <v>-0.02160833932857786</v>
+        <v>-0.01504384658364966</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="20" t="inlineStr">
         <is>
-          <t>Novartis</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="B37" s="22" t="n">
+        <v>-0.001220532879461445</v>
+      </c>
+      <c r="C37" s="22" t="n">
+        <v>-0.009305285902784788</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0.08039093539927578</v>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>Bachem</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>0.006035003128650462</v>
+      </c>
+      <c r="H37" s="22" t="n">
+        <v>-0.03081397123115004</v>
+      </c>
+      <c r="I37" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C37" s="22" t="n">
-        <v>0.00110647077337056</v>
-      </c>
-      <c r="D37" s="22" t="n">
-        <v>0.07778004570472752</v>
-      </c>
-      <c r="F37" s="20" t="inlineStr">
-        <is>
-          <t>Bachem</t>
-        </is>
-      </c>
-      <c r="G37" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="22" t="n">
-        <v>-0.03662792471952214</v>
-      </c>
-      <c r="I37" s="22" t="n">
-        <v>-0.005998800349771405</v>
-      </c>
       <c r="K37" s="29" t="inlineStr">
         <is>
           <t>Alvotech</t>
         </is>
       </c>
       <c r="L37" s="31" t="n">
-        <v>0</v>
+        <v>0.02813855360630302</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>-0.09765625218278728</v>
+        <v>-0.07226560426352036</v>
       </c>
       <c r="N37" s="31" t="n">
-        <v>-0.2048192889742363</v>
+        <v>-0.1824440539103397</v>
       </c>
       <c r="P37" s="20" t="inlineStr">
         <is>
-          <t>패썸 파마</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="Q37" s="22" t="n">
-        <v>0</v>
+        <v>0.06877830006908736</v>
       </c>
       <c r="R37" s="22" t="n">
-        <v>-0.1874144864956259</v>
+        <v>-0.007562958134337272</v>
       </c>
       <c r="S37" s="22" t="n">
-        <v>-0.1496063072754973</v>
+        <v>-0.1410908785733309</v>
       </c>
     </row>
     <row r="38">
@@ -18611,13 +19509,13 @@
         </is>
       </c>
       <c r="B38" s="22" t="n">
-        <v>0</v>
+        <v>0.0003356267615282071</v>
       </c>
       <c r="C38" s="22" t="n">
-        <v>-0.01062768808826275</v>
+        <v>-0.01029562826327013</v>
       </c>
       <c r="D38" s="22" t="n">
-        <v>0.05713273928019991</v>
+        <v>0.05748754131799005</v>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
@@ -18625,13 +19523,13 @@
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>-0.01490412303544431</v>
+        <v>-0.01561388959220589</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-0.08503621724452415</v>
+        <v>-0.0856954532730505</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>-0.1362787449432116</v>
+        <v>-0.1369010604716172</v>
       </c>
       <c r="K38" s="26" t="inlineStr">
         <is>
@@ -18639,27 +19537,27 @@
         </is>
       </c>
       <c r="L38" s="28" t="n">
-        <v>0.0009594059041355019</v>
+        <v>0.008224652082595596</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>-0.02295382891127062</v>
+        <v>-0.01629167691235172</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>-0.01546220143188415</v>
+        <v>-0.008717422636841055</v>
       </c>
       <c r="P38" s="20" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>패썸 파마</t>
         </is>
       </c>
       <c r="Q38" s="22" t="n">
-        <v>0</v>
+        <v>0.008417460171052937</v>
       </c>
       <c r="R38" s="22" t="n">
-        <v>-0.07142852563388491</v>
+        <v>-0.1805745803001282</v>
       </c>
       <c r="S38" s="22" t="n">
-        <v>-0.1963636224920099</v>
+        <v>-0.1424481522372741</v>
       </c>
     </row>
     <row r="39">
@@ -18669,13 +19567,13 @@
         </is>
       </c>
       <c r="B39" s="22" t="n">
-        <v>0</v>
+        <v>-0.01150758895521187</v>
       </c>
       <c r="C39" s="22" t="n">
-        <v>0.01919198017894042</v>
+        <v>0.007463537804592857</v>
       </c>
       <c r="D39" s="22" t="n">
-        <v>0.05345004365192629</v>
+        <v>0.04132737356472971</v>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
@@ -18683,27 +19581,27 @@
         </is>
       </c>
       <c r="G39" s="31" t="n">
-        <v>-0.02483667029298375</v>
+        <v>-0.02701528621448235</v>
       </c>
       <c r="H39" s="31" t="n">
-        <v>-0.1056943255977166</v>
+        <v>-0.1076922971390837</v>
       </c>
       <c r="I39" s="31" t="n">
-        <v>-0.1522727468125422</v>
+        <v>-0.1541666573346262</v>
       </c>
       <c r="P39" s="20" t="inlineStr">
         <is>
-          <t>메타비아</t>
+          <t>Axsome</t>
         </is>
       </c>
       <c r="Q39" s="22" t="n">
-        <v>0</v>
+        <v>-0.01291129141936187</v>
       </c>
       <c r="R39" s="22" t="n">
-        <v>-0.05813948115679957</v>
+        <v>-0.1089109204373395</v>
       </c>
       <c r="S39" s="22" t="n">
-        <v>-0.2546012043356199</v>
+        <v>-0.2649263417342519</v>
       </c>
     </row>
     <row r="40">
@@ -18713,13 +19611,13 @@
         </is>
       </c>
       <c r="B40" s="22" t="n">
-        <v>0</v>
+        <v>-0.003131112567315242</v>
       </c>
       <c r="C40" s="22" t="n">
-        <v>0.009282982344273494</v>
+        <v>0.00612280371427798</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>0.02796216888450154</v>
+        <v>0.02474350361878264</v>
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
@@ -18727,13 +19625,13 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>-0.01335140022755585</v>
+        <v>-0.01157585525890159</v>
       </c>
       <c r="H40" s="28" t="n">
-        <v>-0.02762519359198526</v>
+        <v>-0.02518823410878363</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>-0.01090306160498198</v>
+        <v>-0.00826812553273683</v>
       </c>
       <c r="K40" s="19" t="inlineStr">
         <is>
@@ -18742,17 +19640,17 @@
       </c>
       <c r="P40" s="20" t="inlineStr">
         <is>
-          <t>Axsome</t>
+          <t>메타비아</t>
         </is>
       </c>
       <c r="Q40" s="22" t="n">
-        <v>0</v>
+        <v>-0.05349798801215722</v>
       </c>
       <c r="R40" s="22" t="n">
-        <v>-0.09725532080700039</v>
+        <v>-0.1085271239029972</v>
       </c>
       <c r="S40" s="22" t="n">
-        <v>-0.2553114508596389</v>
+        <v>-0.2944785401703494</v>
       </c>
     </row>
     <row r="41">
@@ -18762,13 +19660,13 @@
         </is>
       </c>
       <c r="B41" s="22" t="n">
-        <v>0</v>
+        <v>-0.01175575994412004</v>
       </c>
       <c r="C41" s="22" t="n">
-        <v>-0.005590785629904005</v>
+        <v>-0.01728082164025979</v>
       </c>
       <c r="D41" s="22" t="n">
-        <v>0.02515071902599586</v>
+        <v>0.01309929326658432</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -18796,13 +19694,13 @@
         </is>
       </c>
       <c r="Q41" s="22" t="n">
-        <v>0</v>
+        <v>0.005025134190656866</v>
       </c>
       <c r="R41" s="22" t="n">
-        <v>-0.3501451308246716</v>
+        <v>-0.3468795229026137</v>
       </c>
       <c r="S41" s="22" t="n">
-        <v>-0.3282070536414262</v>
+        <v>-0.3248312039376375</v>
       </c>
     </row>
     <row r="42">
@@ -18812,13 +19710,13 @@
         </is>
       </c>
       <c r="B42" s="22" t="n">
-        <v>0</v>
+        <v>0.002392880400343245</v>
       </c>
       <c r="C42" s="22" t="n">
-        <v>0.009420274765078229</v>
+        <v>0.01183569675627272</v>
       </c>
       <c r="D42" s="22" t="n">
-        <v>0.003120524930182222</v>
+        <v>0.005520872373469654</v>
       </c>
       <c r="F42" s="19" t="inlineStr">
         <is>
@@ -18827,17 +19725,17 @@
       </c>
       <c r="K42" s="29" t="inlineStr">
         <is>
-          <t>Ionis</t>
+          <t>Dyne</t>
         </is>
       </c>
       <c r="L42" s="31" t="n">
-        <v>0</v>
+        <v>0.07760815816190814</v>
       </c>
       <c r="M42" s="31" t="n">
-        <v>-0.04361240727723215</v>
+        <v>0.04118008957856145</v>
       </c>
       <c r="N42" s="31" t="n">
-        <v>-0.0116094271042011</v>
+        <v>0.04374621145081425</v>
       </c>
       <c r="P42" s="29" t="inlineStr">
         <is>
@@ -18845,13 +19743,13 @@
         </is>
       </c>
       <c r="Q42" s="31" t="n">
-        <v>0</v>
+        <v>0.005847901033519065</v>
       </c>
       <c r="R42" s="31" t="n">
-        <v>-0.04646840049853418</v>
+        <v>-0.04089224207231656</v>
       </c>
       <c r="S42" s="31" t="n">
-        <v>-0.4150513287716457</v>
+        <v>-0.411630606832614</v>
       </c>
     </row>
     <row r="43">
@@ -18861,13 +19759,13 @@
         </is>
       </c>
       <c r="B43" s="22" t="n">
-        <v>0</v>
+        <v>0.009125134452685701</v>
       </c>
       <c r="C43" s="22" t="n">
-        <v>0.02675818489116222</v>
+        <v>0.03612749137868954</v>
       </c>
       <c r="D43" s="22" t="n">
-        <v>-0.01066250136193625</v>
+        <v>-0.001634663667780312</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -18891,17 +19789,17 @@
       </c>
       <c r="K43" s="20" t="inlineStr">
         <is>
-          <t>Dyne</t>
+          <t>Ionis</t>
         </is>
       </c>
       <c r="L43" s="22" t="n">
-        <v>0</v>
+        <v>0.01243668674112386</v>
       </c>
       <c r="M43" s="22" t="n">
-        <v>-0.0338045590203051</v>
+        <v>-0.03171811438344163</v>
       </c>
       <c r="N43" s="22" t="n">
-        <v>-0.03142324643203576</v>
+        <v>0.0006828768287838738</v>
       </c>
       <c r="P43" s="26" t="inlineStr">
         <is>
@@ -18909,13 +19807,13 @@
         </is>
       </c>
       <c r="Q43" s="28" t="n">
-        <v>0</v>
+        <v>0.003787311461334886</v>
       </c>
       <c r="R43" s="28" t="n">
-        <v>-0.07415634109644316</v>
+        <v>-0.07010762089852787</v>
       </c>
       <c r="S43" s="28" t="n">
-        <v>-0.1155846113228909</v>
+        <v>-0.1110949873619838</v>
       </c>
     </row>
     <row r="44">
@@ -18925,13 +19823,13 @@
         </is>
       </c>
       <c r="B44" s="31" t="n">
-        <v>0</v>
+        <v>0.008605410060556595</v>
       </c>
       <c r="C44" s="31" t="n">
-        <v>-0.05185436468752047</v>
+        <v>-0.04369518269852968</v>
       </c>
       <c r="D44" s="31" t="n">
-        <v>-0.0504457126440726</v>
+        <v>-0.04227440862661525</v>
       </c>
       <c r="F44" s="29" t="inlineStr">
         <is>
@@ -18939,13 +19837,13 @@
         </is>
       </c>
       <c r="G44" s="31" t="n">
-        <v>0</v>
+        <v>-0.005919258816848183</v>
       </c>
       <c r="H44" s="31" t="n">
-        <v>0.2452055351919236</v>
+        <v>0.2269406950092752</v>
       </c>
       <c r="I44" s="31" t="n">
-        <v>0.2887523834646075</v>
+        <v>0.2698487923274542</v>
       </c>
       <c r="K44" s="20" t="inlineStr">
         <is>
@@ -18953,13 +19851,13 @@
         </is>
       </c>
       <c r="L44" s="22" t="n">
-        <v>0</v>
+        <v>-0.003821533699295832</v>
       </c>
       <c r="M44" s="22" t="n">
-        <v>-0.0132200726583156</v>
+        <v>-0.01699108540444061</v>
       </c>
       <c r="N44" s="22" t="n">
-        <v>-0.0764674506704589</v>
+        <v>-0.07999676143011825</v>
       </c>
     </row>
     <row r="45">
@@ -18969,13 +19867,13 @@
         </is>
       </c>
       <c r="B45" s="28" t="n">
-        <v>0</v>
+        <v>0.002317336136480201</v>
       </c>
       <c r="C45" s="28" t="n">
-        <v>0.001146048449818656</v>
+        <v>0.003449608790268214</v>
       </c>
       <c r="D45" s="28" t="n">
-        <v>0.04673335876321988</v>
+        <v>0.04916577383710172</v>
       </c>
       <c r="F45" s="20" t="inlineStr">
         <is>
@@ -18983,13 +19881,13 @@
         </is>
       </c>
       <c r="G45" s="22" t="n">
-        <v>0</v>
+        <v>0.009125134452685701</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>0.02675818489116222</v>
+        <v>0.03612749137868954</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>-0.01066250136193625</v>
+        <v>-0.001634663667780312</v>
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
@@ -18997,13 +19895,13 @@
         </is>
       </c>
       <c r="L45" s="22" t="n">
-        <v>0</v>
+        <v>0.0008477320693218715</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>0.001018353278270157</v>
+        <v>0.00186694863832404</v>
       </c>
       <c r="N45" s="22" t="n">
-        <v>-0.1191756220332268</v>
+        <v>-0.1184289189605838</v>
       </c>
       <c r="P45" s="19" t="inlineStr">
         <is>
@@ -19018,13 +19916,13 @@
         </is>
       </c>
       <c r="G46" s="22" t="n">
-        <v>0</v>
+        <v>0.01512654932004631</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>-0.0004483668610782976</v>
+        <v>0.01467140021553059</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>-0.08087161367073403</v>
+        <v>-0.06696837280346968</v>
       </c>
       <c r="K46" s="29" t="inlineStr">
         <is>
@@ -19032,13 +19930,13 @@
         </is>
       </c>
       <c r="L46" s="31" t="n">
-        <v>0</v>
+        <v>0.07476635722262714</v>
       </c>
       <c r="M46" s="31" t="n">
-        <v>-0.06140351855621518</v>
+        <v>0.008771921263311722</v>
       </c>
       <c r="N46" s="31" t="n">
-        <v>-0.1873417723047067</v>
+        <v>-0.1265822769529333</v>
       </c>
       <c r="P46" s="5" t="inlineStr">
         <is>
@@ -19069,17 +19967,17 @@
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>IMVT</t>
         </is>
       </c>
       <c r="G47" s="22" t="n">
-        <v>-0.007782101167315147</v>
+        <v>0.0252040852875306</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>-0.07942238267148016</v>
+        <v>0.01014337204025728</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>-0.1791845493562232</v>
+        <v>-0.1638680256147969</v>
       </c>
       <c r="K47" s="26" t="inlineStr">
         <is>
@@ -19087,13 +19985,13 @@
         </is>
       </c>
       <c r="L47" s="28" t="n">
-        <v>0</v>
+        <v>0.03236748009913704</v>
       </c>
       <c r="M47" s="28" t="n">
-        <v>-0.03020444084675957</v>
+        <v>0.0006219519384629945</v>
       </c>
       <c r="N47" s="28" t="n">
-        <v>-0.08520350370892586</v>
+        <v>-0.05611577381280745</v>
       </c>
       <c r="P47" s="20" t="inlineStr">
         <is>
@@ -19101,13 +19999,13 @@
         </is>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>0</v>
+        <v>0.002301875111573759</v>
       </c>
       <c r="R47" s="22" t="n">
-        <v>-0.004681753397356769</v>
+        <v>-0.00239065509740688</v>
       </c>
       <c r="S47" s="22" t="n">
-        <v>-0.0005001805656420499</v>
+        <v>0.00180054319273637</v>
       </c>
     </row>
     <row r="48">
@@ -19133,17 +20031,17 @@
       </c>
       <c r="F48" s="29" t="inlineStr">
         <is>
-          <t>IMVT</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="G48" s="31" t="n">
-        <v>0</v>
+        <v>-0.007782101167315147</v>
       </c>
       <c r="H48" s="31" t="n">
-        <v>-0.01469045379686462</v>
+        <v>-0.07942238267148016</v>
       </c>
       <c r="I48" s="31" t="n">
-        <v>-0.1844238758074203</v>
+        <v>-0.1791845493562232</v>
       </c>
       <c r="P48" s="20" t="inlineStr">
         <is>
@@ -19151,13 +20049,13 @@
         </is>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>0</v>
+        <v>0.004449384079133534</v>
       </c>
       <c r="R48" s="22" t="n">
-        <v>-0.1944444539394099</v>
+        <v>-0.1908602279179101</v>
       </c>
       <c r="S48" s="22" t="n">
-        <v>-0.2023070624699809</v>
+        <v>-0.1987578202136975</v>
       </c>
     </row>
     <row r="49">
@@ -19167,13 +20065,13 @@
         </is>
       </c>
       <c r="B49" s="31" t="n">
-        <v>0</v>
+        <v>0.2049861581830046</v>
       </c>
       <c r="C49" s="31" t="n">
-        <v>-0.07908167733792526</v>
+        <v>0.1096938316249101</v>
       </c>
       <c r="D49" s="31" t="n">
-        <v>0.1533545569025148</v>
+        <v>0.3897762765448229</v>
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
@@ -19181,13 +20079,13 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>-0.001556420233463029</v>
+        <v>0.007150881815219856</v>
       </c>
       <c r="H49" s="28" t="n">
-        <v>0.03548050335073254</v>
+        <v>0.04169211519445448</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>-0.03327803134634124</v>
+        <v>-0.02836136382296317</v>
       </c>
       <c r="K49" s="19" t="inlineStr">
         <is>
@@ -19200,13 +20098,13 @@
         </is>
       </c>
       <c r="Q49" s="28" t="n">
-        <v>0</v>
+        <v>0.003375629595353646</v>
       </c>
       <c r="R49" s="28" t="n">
-        <v>-0.09956310366838333</v>
+        <v>-0.0966254415076585</v>
       </c>
       <c r="S49" s="28" t="n">
-        <v>-0.1014036215178115</v>
+        <v>-0.09847863851048055</v>
       </c>
     </row>
     <row r="50">
@@ -19216,13 +20114,13 @@
         </is>
       </c>
       <c r="B50" s="22" t="n">
-        <v>0</v>
+        <v>0.09058609976517262</v>
       </c>
       <c r="C50" s="22" t="n">
-        <v>-0.04898647941142831</v>
+        <v>0.03716212624263604</v>
       </c>
       <c r="D50" s="22" t="n">
-        <v>-0.08678018665409748</v>
+        <v>-0.004055165534813332</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -19252,13 +20150,13 @@
         </is>
       </c>
       <c r="B51" s="22" t="n">
-        <v>0</v>
+        <v>0.08333325054910778</v>
       </c>
       <c r="C51" s="22" t="n">
-        <v>-0.06976737738815952</v>
+        <v>0.007751930820906638</v>
       </c>
       <c r="D51" s="22" t="n">
-        <v>-0.1078066749755687</v>
+        <v>-0.03345730508306632</v>
       </c>
       <c r="F51" s="19" t="inlineStr">
         <is>
@@ -19271,13 +20169,13 @@
         </is>
       </c>
       <c r="L51" s="22" t="n">
-        <v>0</v>
+        <v>0.05724137404869345</v>
       </c>
       <c r="M51" s="22" t="n">
-        <v>-0.09881915087068271</v>
+        <v>-0.04723432080015233</v>
       </c>
       <c r="N51" s="22" t="n">
-        <v>-0.1185410743160967</v>
+        <v>-0.06808515424246497</v>
       </c>
       <c r="P51" s="19" t="inlineStr">
         <is>
@@ -19292,13 +20190,13 @@
         </is>
       </c>
       <c r="B52" s="31" t="n">
-        <v>0</v>
+        <v>0.05019389886591941</v>
       </c>
       <c r="C52" s="31" t="n">
-        <v>-0.01744191515541416</v>
+        <v>0.03187650598516667</v>
       </c>
       <c r="D52" s="31" t="n">
-        <v>-0.1210545230126614</v>
+        <v>-0.07693682263210155</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -19326,13 +20224,13 @@
         </is>
       </c>
       <c r="L52" s="22" t="n">
-        <v>-0.03448277738995775</v>
+        <v>-0.03864447156916506</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>-0.1115974223999187</v>
+        <v>-0.1154267273044924</v>
       </c>
       <c r="N52" s="22" t="n">
-        <v>-0.1671795184795674</v>
+        <v>-0.1707692464192708</v>
       </c>
       <c r="P52" s="5" t="inlineStr">
         <is>
@@ -19362,13 +20260,13 @@
         </is>
       </c>
       <c r="B53" s="28" t="n">
-        <v>0</v>
+        <v>0.1072748518408011</v>
       </c>
       <c r="C53" s="28" t="n">
-        <v>-0.05381936232323181</v>
+        <v>0.04662109866840486</v>
       </c>
       <c r="D53" s="28" t="n">
-        <v>-0.04057170693495321</v>
+        <v>0.06883174582371043</v>
       </c>
       <c r="F53" s="29" t="inlineStr">
         <is>
@@ -19376,13 +20274,13 @@
         </is>
       </c>
       <c r="G53" s="31" t="n">
-        <v>0</v>
+        <v>0.002165532701290163</v>
       </c>
       <c r="H53" s="31" t="n">
-        <v>-0.003521196742826471</v>
+        <v>-0.001363289308230486</v>
       </c>
       <c r="I53" s="31" t="n">
-        <v>0.1113389564647451</v>
+        <v>0.1137455973171873</v>
       </c>
       <c r="K53" s="26" t="inlineStr">
         <is>
@@ -19390,13 +20288,13 @@
         </is>
       </c>
       <c r="L53" s="28" t="n">
-        <v>-0.01724138869497888</v>
+        <v>0.009298451239764194</v>
       </c>
       <c r="M53" s="28" t="n">
-        <v>-0.1052082866353007</v>
+        <v>-0.08133052405232238</v>
       </c>
       <c r="N53" s="28" t="n">
-        <v>-0.142860296397832</v>
+        <v>-0.1194272003308679</v>
       </c>
       <c r="P53" s="29" t="inlineStr">
         <is>
@@ -19404,13 +20302,13 @@
         </is>
       </c>
       <c r="Q53" s="31" t="n">
-        <v>0</v>
+        <v>-0.01538559232990289</v>
       </c>
       <c r="R53" s="31" t="n">
-        <v>0.005683347638030689</v>
+        <v>-0.009789686361700078</v>
       </c>
       <c r="S53" s="31" t="n">
-        <v>0.1197147465874504</v>
+        <v>0.1024872719706755</v>
       </c>
     </row>
     <row r="54">
@@ -19420,13 +20318,13 @@
         </is>
       </c>
       <c r="G54" s="22" t="n">
-        <v>0</v>
+        <v>0.00746689896713959</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>0.01296305283127119</v>
+        <v>0.02052674560420753</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>0.09490509220240506</v>
+        <v>0.1030806379044871</v>
       </c>
       <c r="P54" s="20" t="inlineStr">
         <is>
@@ -19434,13 +20332,13 @@
         </is>
       </c>
       <c r="Q54" s="22" t="n">
-        <v>0</v>
+        <v>-0.008861736039371237</v>
       </c>
       <c r="R54" s="22" t="n">
-        <v>0.001690834479059378</v>
+        <v>-0.007185885289151428</v>
       </c>
       <c r="S54" s="22" t="n">
-        <v>0.0614781374709199</v>
+        <v>0.05207159840508924</v>
       </c>
     </row>
     <row r="55">
@@ -19455,13 +20353,13 @@
         </is>
       </c>
       <c r="G55" s="22" t="n">
-        <v>0</v>
+        <v>0.005501864514392052</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>0.01471830355103076</v>
+        <v>0.02030114617744228</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>0.08935702953563585</v>
+        <v>0.09535052431994151</v>
       </c>
       <c r="K55" s="19" t="inlineStr">
         <is>
@@ -19474,13 +20372,13 @@
         </is>
       </c>
       <c r="Q55" s="22" t="n">
-        <v>0</v>
+        <v>-0.01140852209025989</v>
       </c>
       <c r="R55" s="22" t="n">
-        <v>0</v>
+        <v>-0.01140852209025989</v>
       </c>
       <c r="S55" s="22" t="n">
-        <v>0.02151508117773449</v>
+        <v>0.009861103808584515</v>
       </c>
     </row>
     <row r="56">
@@ -19510,13 +20408,13 @@
         </is>
       </c>
       <c r="G56" s="22" t="n">
-        <v>0</v>
+        <v>-0.01175575994412004</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>-0.005590785629904005</v>
+        <v>-0.01728082164025979</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>0.02515071902599586</v>
+        <v>0.01309929326658432</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -19544,13 +20442,13 @@
         </is>
       </c>
       <c r="Q56" s="31" t="n">
-        <v>0</v>
+        <v>-0.01697176607466844</v>
       </c>
       <c r="R56" s="31" t="n">
-        <v>0.02371889094738977</v>
+        <v>0.006344573404011733</v>
       </c>
       <c r="S56" s="31" t="n">
-        <v>0.01343124377563698</v>
+        <v>-0.003768474226483409</v>
       </c>
     </row>
     <row r="57">
@@ -19560,41 +20458,41 @@
         </is>
       </c>
       <c r="B57" s="22" t="n">
+        <v>-0.01416261133246932</v>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>0.0006249745686848218</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>0.05699824451723301</v>
+      </c>
+      <c r="F57" s="20" t="inlineStr">
+        <is>
+          <t>Kailera</t>
+        </is>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>0.02819104493127722</v>
+      </c>
+      <c r="H57" s="22" t="n">
+        <v>0.01861906630921761</v>
+      </c>
+      <c r="I57" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="C57" s="22" t="n">
-        <v>0.01500002543131518</v>
-      </c>
-      <c r="D57" s="22" t="n">
-        <v>0.0721831578592127</v>
-      </c>
-      <c r="F57" s="20" t="inlineStr">
-        <is>
-          <t>Kailera</t>
-        </is>
-      </c>
-      <c r="G57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="22" t="n">
-        <v>-0.009309533154608807</v>
-      </c>
-      <c r="I57" s="22" t="n">
-        <v>-0.02741810004108858</v>
-      </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
           <t>탠덤</t>
         </is>
       </c>
       <c r="L57" s="22" t="n">
-        <v>0</v>
+        <v>0.01693120112608248</v>
       </c>
       <c r="M57" s="22" t="n">
-        <v>0.1440677418170475</v>
+        <v>0.1634381828556148</v>
       </c>
       <c r="N57" s="22" t="n">
-        <v>0.1538461896750021</v>
+        <v>0.1733821915809535</v>
       </c>
       <c r="P57" s="26" t="inlineStr">
         <is>
@@ -19602,13 +20500,13 @@
         </is>
       </c>
       <c r="Q57" s="28" t="n">
-        <v>0</v>
+        <v>-0.01315690413355061</v>
       </c>
       <c r="R57" s="28" t="n">
-        <v>0.007773268266119959</v>
+        <v>-0.005509880084274915</v>
       </c>
       <c r="S57" s="28" t="n">
-        <v>0.05403480225293544</v>
+        <v>0.04016287498946647</v>
       </c>
     </row>
     <row r="58">
@@ -19618,13 +20516,13 @@
         </is>
       </c>
       <c r="B58" s="22" t="n">
-        <v>0</v>
+        <v>-0.002035975106907228</v>
       </c>
       <c r="C58" s="22" t="n">
-        <v>0.01169431566003953</v>
+        <v>0.009634531217556086</v>
       </c>
       <c r="D58" s="22" t="n">
-        <v>0.02760340411982165</v>
+        <v>0.02551122916926052</v>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
@@ -19632,13 +20530,13 @@
         </is>
       </c>
       <c r="G58" s="22" t="n">
-        <v>0</v>
+        <v>0.005916746003726825</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>-0.06373789999981072</v>
+        <v>-0.05819827496119379</v>
       </c>
       <c r="I58" s="22" t="n">
-        <v>-0.1467389700808536</v>
+        <v>-0.1416904412919436</v>
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
@@ -19646,13 +20544,13 @@
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>0</v>
+        <v>0.003818888819486332</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>0.04641050999379015</v>
+        <v>0.05040663539099843</v>
       </c>
       <c r="N58" s="22" t="n">
-        <v>0.09355988350598632</v>
+        <v>0.09773606711854632</v>
       </c>
     </row>
     <row r="59">
@@ -19662,13 +20560,13 @@
         </is>
       </c>
       <c r="B59" s="22" t="n">
-        <v>0</v>
+        <v>-0.0008184387498314516</v>
       </c>
       <c r="C59" s="22" t="n">
-        <v>0.05573343355975502</v>
+        <v>0.04270766435618056</v>
       </c>
       <c r="D59" s="22" t="n">
-        <v>0.017074634970909</v>
+        <v>0.004525842788331014</v>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
@@ -19676,13 +20574,13 @@
         </is>
       </c>
       <c r="G59" s="22" t="n">
-        <v>0</v>
+        <v>0.02132695959503472</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>-0.07779715229837603</v>
+        <v>-0.05812936942701763</v>
       </c>
       <c r="I59" s="22" t="n">
-        <v>-0.41307371533573</v>
+        <v>-0.4005563621774313</v>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
@@ -19690,13 +20588,13 @@
         </is>
       </c>
       <c r="L59" s="22" t="n">
-        <v>0</v>
+        <v>-0.0001273022307409777</v>
       </c>
       <c r="M59" s="22" t="n">
-        <v>-0.08362489325387634</v>
+        <v>-0.0837415498491606</v>
       </c>
       <c r="N59" s="22" t="n">
-        <v>-0.1044112995737784</v>
+        <v>-0.104525310013169</v>
       </c>
       <c r="P59" s="19" t="inlineStr">
         <is>
@@ -19711,13 +20609,13 @@
         </is>
       </c>
       <c r="B60" s="28" t="n">
-        <v>0</v>
+        <v>-0.005672341729736001</v>
       </c>
       <c r="C60" s="28" t="n">
-        <v>0.02747592488370324</v>
+        <v>0.01765572338080716</v>
       </c>
       <c r="D60" s="28" t="n">
-        <v>0.03895373231664778</v>
+        <v>0.02901177215827485</v>
       </c>
       <c r="F60" s="29" t="inlineStr">
         <is>
@@ -19725,13 +20623,13 @@
         </is>
       </c>
       <c r="G60" s="31" t="n">
-        <v>0</v>
+        <v>0.02808758078854723</v>
       </c>
       <c r="H60" s="31" t="n">
-        <v>-0.09359790661517942</v>
+        <v>-0.06813926459032493</v>
       </c>
       <c r="I60" s="31" t="n">
-        <v>-0.418727534273199</v>
+        <v>-0.4024009969319394</v>
       </c>
       <c r="K60" s="26" t="inlineStr">
         <is>
@@ -19739,13 +20637,13 @@
         </is>
       </c>
       <c r="L60" s="28" t="n">
-        <v>0</v>
+        <v>0.00687426257160928</v>
       </c>
       <c r="M60" s="28" t="n">
-        <v>0.03561778618565378</v>
+        <v>0.04336775613248423</v>
       </c>
       <c r="N60" s="28" t="n">
-        <v>0.04766492453573667</v>
+        <v>0.05553098289544359</v>
       </c>
       <c r="P60" s="5" t="inlineStr">
         <is>
@@ -19775,13 +20673,13 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>0</v>
+        <v>0.01086260844466097</v>
       </c>
       <c r="H61" s="28" t="n">
-        <v>-0.02823413975730044</v>
+        <v>-0.0179580077295199</v>
       </c>
       <c r="I61" s="28" t="n">
-        <v>-0.08565081531276117</v>
+        <v>-0.07742146844913927</v>
       </c>
       <c r="P61" s="20" t="inlineStr">
         <is>
@@ -19789,13 +20687,13 @@
         </is>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>0</v>
+        <v>0.006600660066006681</v>
       </c>
       <c r="R61" s="22" t="n">
-        <v>-0.004608275025469788</v>
+        <v>0.003950007423466406</v>
       </c>
       <c r="S61" s="22" t="n">
-        <v>0.02093174015509369</v>
+        <v>0.02970961320156174</v>
       </c>
     </row>
     <row r="62">
@@ -19815,13 +20713,13 @@
         </is>
       </c>
       <c r="Q62" s="22" t="n">
-        <v>0</v>
+        <v>-0.01020410645757752</v>
       </c>
       <c r="R62" s="22" t="n">
-        <v>-0.02970297497144536</v>
+        <v>-0.03960398911030749</v>
       </c>
       <c r="S62" s="22" t="n">
-        <v>-0.03312186943290918</v>
+        <v>-0.04298799680871934</v>
       </c>
     </row>
     <row r="63">
@@ -19876,13 +20774,13 @@
         </is>
       </c>
       <c r="Q63" s="22" t="n">
+        <v>0.02789397589079434</v>
+      </c>
+      <c r="R63" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="R63" s="22" t="n">
-        <v>-0.02713701660389711</v>
-      </c>
       <c r="S63" s="22" t="n">
-        <v>-0.1037499904632568</v>
+        <v>-0.07875001430511475</v>
       </c>
     </row>
     <row r="64">
@@ -19892,13 +20790,13 @@
         </is>
       </c>
       <c r="B64" s="22" t="n">
-        <v>0</v>
+        <v>-0.005637000155576888</v>
       </c>
       <c r="C64" s="22" t="n">
-        <v>0.05272519794110297</v>
+        <v>0.04502371248028658</v>
       </c>
       <c r="D64" s="22" t="n">
-        <v>0.1584094055413574</v>
+        <v>0.1499347597250533</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -19926,13 +20824,13 @@
         </is>
       </c>
       <c r="L64" s="22" t="n">
-        <v>0</v>
+        <v>-0.01273166073518961</v>
       </c>
       <c r="M64" s="22" t="n">
-        <v>0.03111873260916087</v>
+        <v>0.01799087872788241</v>
       </c>
       <c r="N64" s="22" t="n">
-        <v>0.1338940967218005</v>
+        <v>0.1194577417727043</v>
       </c>
       <c r="P64" s="26" t="inlineStr">
         <is>
@@ -19940,13 +20838,13 @@
         </is>
       </c>
       <c r="Q64" s="28" t="n">
-        <v>0</v>
+        <v>0.008096843166407833</v>
       </c>
       <c r="R64" s="28" t="n">
-        <v>-0.02048275553360409</v>
+        <v>-0.01188466056228036</v>
       </c>
       <c r="S64" s="28" t="n">
-        <v>-0.03864670658035744</v>
+        <v>-0.03067613263742412</v>
       </c>
     </row>
     <row r="65">
@@ -19956,13 +20854,13 @@
         </is>
       </c>
       <c r="B65" s="22" t="n">
-        <v>0</v>
+        <v>-0.008144016462662051</v>
       </c>
       <c r="C65" s="22" t="n">
-        <v>0.03184425732575957</v>
+        <v>0.02344090070719518</v>
       </c>
       <c r="D65" s="22" t="n">
-        <v>0.07034712520351083</v>
+        <v>0.06163020059509039</v>
       </c>
       <c r="F65" s="20" t="inlineStr">
         <is>
@@ -19970,13 +20868,13 @@
         </is>
       </c>
       <c r="G65" s="22" t="n">
-        <v>0</v>
+        <v>-0.009931472559707832</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>0.01013518333883057</v>
+        <v>0.01037645558459643</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>0.1252688105333224</v>
+        <v>0.125537582612036</v>
       </c>
       <c r="K65" s="26" t="inlineStr">
         <is>
@@ -19984,13 +20882,13 @@
         </is>
       </c>
       <c r="L65" s="28" t="n">
-        <v>0</v>
+        <v>-0.01273166073518961</v>
       </c>
       <c r="M65" s="28" t="n">
-        <v>0.03111873260916087</v>
+        <v>0.01799087872788241</v>
       </c>
       <c r="N65" s="28" t="n">
-        <v>0.1338940967218005</v>
+        <v>0.1194577417727043</v>
       </c>
     </row>
     <row r="66">
@@ -20000,27 +20898,27 @@
         </is>
       </c>
       <c r="B66" s="28" t="n">
-        <v>0</v>
+        <v>-0.00689050830911947</v>
       </c>
       <c r="C66" s="28" t="n">
-        <v>0.04228472763343127</v>
+        <v>0.03423230659374088</v>
       </c>
       <c r="D66" s="28" t="n">
-        <v>0.1143782653724341</v>
+        <v>0.1057824801600719</v>
       </c>
       <c r="F66" s="20" t="inlineStr">
         <is>
-          <t>GE 헬스케어</t>
+          <t>필립스</t>
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>0</v>
+        <v>-0.006021823456899611</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>0.02491812496584811</v>
+        <v>0.01576922490046573</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>0.08912100689081326</v>
+        <v>0.08016355923569374</v>
       </c>
       <c r="P66" s="19" t="inlineStr">
         <is>
@@ -20031,17 +20929,17 @@
     <row r="67">
       <c r="F67" s="20" t="inlineStr">
         <is>
-          <t>필립스</t>
+          <t>GE 헬스케어</t>
         </is>
       </c>
       <c r="G67" s="22" t="n">
-        <v>0</v>
+        <v>-0.01208672834131264</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>0.02192306518554688</v>
+        <v>0.01253021801729837</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>0.08670752007084581</v>
+        <v>0.075957097149707</v>
       </c>
       <c r="K67" s="19" t="inlineStr">
         <is>
@@ -20081,13 +20979,13 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>0</v>
+        <v>-0.00934667478597336</v>
       </c>
       <c r="H68" s="28" t="n">
-        <v>0.01899212449674185</v>
+        <v>0.01289196616745351</v>
       </c>
       <c r="I68" s="28" t="n">
-        <v>0.1003657791649938</v>
+        <v>0.09388607966581224</v>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
@@ -20115,13 +21013,13 @@
         </is>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>0</v>
+        <v>-0.01307191715264577</v>
       </c>
       <c r="R68" s="22" t="n">
-        <v>-0.03096408016904395</v>
+        <v>-0.04363123743101216</v>
       </c>
       <c r="S68" s="22" t="n">
-        <v>0.3317214946382105</v>
+        <v>0.3143133415899024</v>
       </c>
     </row>
     <row r="69">
@@ -20151,13 +21049,13 @@
         </is>
       </c>
       <c r="L69" s="31" t="n">
-        <v>0</v>
+        <v>-0.02452743812525582</v>
       </c>
       <c r="M69" s="31" t="n">
-        <v>-0.002674518290589623</v>
+        <v>-0.02713635733395814</v>
       </c>
       <c r="N69" s="31" t="n">
-        <v>0.139821863427718</v>
+        <v>0.1118649531986808</v>
       </c>
       <c r="P69" s="20" t="inlineStr">
         <is>
@@ -20165,13 +21063,13 @@
         </is>
       </c>
       <c r="Q69" s="22" t="n">
-        <v>0</v>
+        <v>-0.003970632661912776</v>
       </c>
       <c r="R69" s="22" t="n">
-        <v>0.03006129570830196</v>
+        <v>0.02597130068379028</v>
       </c>
       <c r="S69" s="22" t="n">
-        <v>0.1523678789043483</v>
+        <v>0.1477922493658317</v>
       </c>
     </row>
     <row r="70">
@@ -20181,13 +21079,13 @@
         </is>
       </c>
       <c r="B70" s="22" t="n">
-        <v>0</v>
+        <v>-0.03288487725015155</v>
       </c>
       <c r="C70" s="22" t="n">
-        <v>-0.001052045591787398</v>
+        <v>-0.03390232645179148</v>
       </c>
       <c r="D70" s="22" t="n">
-        <v>0.06593657912137085</v>
+        <v>0.03088338556051817</v>
       </c>
       <c r="F70" s="19" t="inlineStr">
         <is>
@@ -20200,13 +21098,13 @@
         </is>
       </c>
       <c r="L70" s="22" t="n">
-        <v>0</v>
+        <v>-0.005680444634133974</v>
       </c>
       <c r="M70" s="22" t="n">
-        <v>-0.02377276322249855</v>
+        <v>-0.02931816799134668</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>0.1132397742132407</v>
+        <v>0.1069160773113067</v>
       </c>
       <c r="P70" s="26" t="inlineStr">
         <is>
@@ -20214,13 +21112,13 @@
         </is>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>0</v>
+        <v>-0.008521274907279275</v>
       </c>
       <c r="R70" s="28" t="n">
-        <v>-0.000451392230370995</v>
+        <v>-0.008829968373610941</v>
       </c>
       <c r="S70" s="28" t="n">
-        <v>0.2420446867712794</v>
+        <v>0.2310527954778671</v>
       </c>
     </row>
     <row r="71">
@@ -20230,13 +21128,13 @@
         </is>
       </c>
       <c r="B71" s="22" t="n">
-        <v>0</v>
+        <v>-0.02565541587985143</v>
       </c>
       <c r="C71" s="22" t="n">
-        <v>-0.01237512862275758</v>
+        <v>-0.0377130554312255</v>
       </c>
       <c r="D71" s="22" t="n">
-        <v>0.04878337874951244</v>
+        <v>0.02187640499981791</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -20264,13 +21162,13 @@
         </is>
       </c>
       <c r="L71" s="22" t="n">
-        <v>0</v>
+        <v>-0.0007548028959820652</v>
       </c>
       <c r="M71" s="22" t="n">
-        <v>-0.02041691875974283</v>
+        <v>-0.02115631090631809</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>0.1061434532444232</v>
+        <v>0.1053085329625425</v>
       </c>
     </row>
     <row r="72">
@@ -20280,13 +21178,13 @@
         </is>
       </c>
       <c r="B72" s="28" t="n">
-        <v>0</v>
+        <v>-0.02927014656500149</v>
       </c>
       <c r="C72" s="28" t="n">
-        <v>-0.00671358710727249</v>
+        <v>-0.03580769094150849</v>
       </c>
       <c r="D72" s="28" t="n">
-        <v>0.05735997893544165</v>
+        <v>0.02637989528016804</v>
       </c>
       <c r="F72" s="29" t="inlineStr">
         <is>
@@ -20294,13 +21192,13 @@
         </is>
       </c>
       <c r="G72" s="31" t="n">
-        <v>0</v>
+        <v>0.1185185088004967</v>
       </c>
       <c r="H72" s="31" t="n">
-        <v>0.0418963756589501</v>
+        <v>0.1653803804266909</v>
       </c>
       <c r="I72" s="31" t="n">
-        <v>-0.03027194250983012</v>
+        <v>0.08465878080590716</v>
       </c>
       <c r="K72" s="29" t="inlineStr">
         <is>
@@ -20308,13 +21206,13 @@
         </is>
       </c>
       <c r="L72" s="31" t="n">
-        <v>0</v>
+        <v>-0.02279054280562187</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>-0.02012809645823321</v>
+        <v>-0.04245990901992802</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>0.08219593026469951</v>
+        <v>0.05753209759193223</v>
       </c>
       <c r="P72" s="19" t="inlineStr">
         <is>
@@ -20325,17 +21223,17 @@
     <row r="73">
       <c r="F73" s="20" t="inlineStr">
         <is>
-          <t>Insilico</t>
+          <t>Twist</t>
         </is>
       </c>
       <c r="G73" s="22" t="n">
-        <v>-0.01666674945089219</v>
+        <v>0.1005163931395223</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>-0.02479346252335912</v>
+        <v>0.1201822671481472</v>
       </c>
       <c r="I73" s="22" t="n">
-        <v>-0.03278695092153661</v>
+        <v>0.008517388665713721</v>
       </c>
       <c r="K73" s="26" t="inlineStr">
         <is>
@@ -20343,13 +21241,13 @@
         </is>
       </c>
       <c r="L73" s="28" t="n">
-        <v>0</v>
+        <v>-0.01343830711524843</v>
       </c>
       <c r="M73" s="28" t="n">
-        <v>-0.01674807418276605</v>
+        <v>-0.03001768631288773</v>
       </c>
       <c r="N73" s="28" t="n">
-        <v>0.1103502552875203</v>
+        <v>0.09540541526611557</v>
       </c>
       <c r="P73" s="5" t="inlineStr">
         <is>
@@ -20380,17 +21278,17 @@
       </c>
       <c r="F74" s="20" t="inlineStr">
         <is>
-          <t>Twist</t>
+          <t>Insilico</t>
         </is>
       </c>
       <c r="G74" s="22" t="n">
-        <v>0</v>
+        <v>-0.01666674945089219</v>
       </c>
       <c r="H74" s="22" t="n">
-        <v>0.01786967839027143</v>
+        <v>-0.02479346252335912</v>
       </c>
       <c r="I74" s="22" t="n">
-        <v>-0.08359621451104104</v>
+        <v>-0.03278695092153661</v>
       </c>
       <c r="P74" s="20" t="inlineStr">
         <is>
@@ -20398,13 +21296,13 @@
         </is>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>0</v>
+        <v>0.03110239230376965</v>
       </c>
       <c r="R74" s="22" t="n">
-        <v>0.01160756897009296</v>
+        <v>0.04307098443766355</v>
       </c>
       <c r="S74" s="22" t="n">
-        <v>0.06132039847557902</v>
+        <v>0.09433000186895968</v>
       </c>
     </row>
     <row r="75">
@@ -20434,13 +21332,13 @@
         </is>
       </c>
       <c r="G75" s="22" t="n">
-        <v>0</v>
+        <v>0.07430014281825903</v>
       </c>
       <c r="H75" s="22" t="n">
-        <v>0.006142376960440066</v>
+        <v>0.08089889926410354</v>
       </c>
       <c r="I75" s="22" t="n">
-        <v>-0.1231230333812673</v>
+        <v>-0.05797094952745363</v>
       </c>
       <c r="P75" s="20" t="inlineStr">
         <is>
@@ -20448,13 +21346,13 @@
         </is>
       </c>
       <c r="Q75" s="22" t="n">
-        <v>0</v>
+        <v>0.02776333367153683</v>
       </c>
       <c r="R75" s="22" t="n">
-        <v>0.06556371180399068</v>
+        <v>0.09514731268308618</v>
       </c>
       <c r="S75" s="22" t="n">
-        <v>-0.01735578016542605</v>
+        <v>0.009925699190248327</v>
       </c>
     </row>
     <row r="76">
@@ -20464,13 +21362,13 @@
         </is>
       </c>
       <c r="B76" s="22" t="n">
-        <v>0</v>
+        <v>0.1005163931395223</v>
       </c>
       <c r="C76" s="22" t="n">
-        <v>0.01786967839027143</v>
+        <v>0.1201822671481472</v>
       </c>
       <c r="D76" s="22" t="n">
-        <v>-0.08359621451104104</v>
+        <v>0.008517388665713721</v>
       </c>
       <c r="F76" s="29" t="inlineStr">
         <is>
@@ -20478,13 +21376,13 @@
         </is>
       </c>
       <c r="G76" s="31" t="n">
-        <v>0</v>
+        <v>0.09061221687161192</v>
       </c>
       <c r="H76" s="31" t="n">
-        <v>0.04700856407701148</v>
+        <v>0.1418803311515928</v>
       </c>
       <c r="I76" s="31" t="n">
-        <v>-0.1618200347694718</v>
+        <v>-0.08587068998256309</v>
       </c>
       <c r="P76" s="26" t="inlineStr">
         <is>
@@ -20492,13 +21390,13 @@
         </is>
       </c>
       <c r="Q76" s="28" t="n">
-        <v>0</v>
+        <v>0.02943286298765324</v>
       </c>
       <c r="R76" s="28" t="n">
-        <v>0.03858564038704182</v>
+        <v>0.06910914856037487</v>
       </c>
       <c r="S76" s="28" t="n">
-        <v>0.02198230915507648</v>
+        <v>0.052127850529604</v>
       </c>
     </row>
     <row r="77">
@@ -20508,13 +21406,13 @@
         </is>
       </c>
       <c r="B77" s="22" t="n">
-        <v>0.04668768159673364</v>
+        <v>0.04100943866791251</v>
       </c>
       <c r="C77" s="22" t="n">
-        <v>-0.007181265018516458</v>
+        <v>-0.01256727085447851</v>
       </c>
       <c r="D77" s="22" t="n">
-        <v>-0.2054597308720009</v>
+        <v>-0.209770083180683</v>
       </c>
       <c r="F77" s="26" t="inlineStr">
         <is>
@@ -20522,13 +21420,13 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>-0.003333349890178439</v>
+        <v>0.07345610243579956</v>
       </c>
       <c r="H77" s="28" t="n">
-        <v>0.01762470651266279</v>
+        <v>0.09670968309343506</v>
       </c>
       <c r="I77" s="28" t="n">
-        <v>-0.08631963521862937</v>
+        <v>-0.01669048419198649</v>
       </c>
     </row>
     <row r="78">
@@ -20538,13 +21436,13 @@
         </is>
       </c>
       <c r="B78" s="28" t="n">
-        <v>0.02334384079836682</v>
+        <v>0.07076291590371742</v>
       </c>
       <c r="C78" s="28" t="n">
-        <v>0.005344206685877484</v>
+        <v>0.05380749814683433</v>
       </c>
       <c r="D78" s="28" t="n">
-        <v>-0.144527972691521</v>
+        <v>-0.1006263472574846</v>
       </c>
     </row>
   </sheetData>
@@ -22316,10 +23214,10 @@
         <v>0.0004239605735966527</v>
       </c>
       <c r="U15" s="22" t="n">
-        <v>0</v>
+        <v>0.002317336136480201</v>
       </c>
       <c r="V15" s="22" t="n">
-        <v>0.04673335876321988</v>
+        <v>0.04916577383710172</v>
       </c>
     </row>
     <row r="16">
@@ -22383,13 +23281,13 @@
         <v>0.01893172614844548</v>
       </c>
       <c r="T16" s="22" t="n">
-        <v>0.00112238400116874</v>
+        <v>0.001800718025942188</v>
       </c>
       <c r="U16" s="22" t="n">
-        <v>-0.01335140022755585</v>
+        <v>-0.01157585525890159</v>
       </c>
       <c r="V16" s="22" t="n">
-        <v>-0.01090306160498198</v>
+        <v>-0.00826812553273683</v>
       </c>
     </row>
     <row r="17">
@@ -22456,10 +23354,10 @@
         <v>0.007934077285872343</v>
       </c>
       <c r="U17" s="22" t="n">
-        <v>0.0009594059041355019</v>
+        <v>0.008224652082595596</v>
       </c>
       <c r="V17" s="22" t="n">
-        <v>-0.01546220143188415</v>
+        <v>-0.008717422636841055</v>
       </c>
     </row>
     <row r="18">
@@ -22523,13 +23421,13 @@
         <v>-0.03886286028860549</v>
       </c>
       <c r="T18" s="22" t="n">
-        <v>-0.03501091089274284</v>
+        <v>-0.03433912145115157</v>
       </c>
       <c r="U18" s="22" t="n">
-        <v>0</v>
+        <v>0.003787311461334886</v>
       </c>
       <c r="V18" s="22" t="n">
-        <v>-0.1155846113228909</v>
+        <v>-0.1110949873619838</v>
       </c>
     </row>
     <row r="19">
@@ -22596,10 +23494,10 @@
         <v>0.01199982353310909</v>
       </c>
       <c r="U19" s="22" t="n">
-        <v>0</v>
+        <v>0.03236748009913704</v>
       </c>
       <c r="V19" s="22" t="n">
-        <v>-0.08520350370892586</v>
+        <v>-0.05611577381280745</v>
       </c>
     </row>
     <row r="20">
@@ -22663,13 +23561,13 @@
         <v>0.0019500824884503</v>
       </c>
       <c r="T20" s="22" t="n">
-        <v>-0.009012266891997212</v>
+        <v>-0.01077246073624276</v>
       </c>
       <c r="U20" s="22" t="n">
-        <v>-0.001556420233463029</v>
+        <v>0.007150881815219856</v>
       </c>
       <c r="V20" s="22" t="n">
-        <v>-0.03327803134634124</v>
+        <v>-0.02836136382296317</v>
       </c>
     </row>
     <row r="21">
@@ -22736,10 +23634,10 @@
         <v>-0.008141983501841532</v>
       </c>
       <c r="U21" s="22" t="n">
-        <v>0</v>
+        <v>0.003375629595353646</v>
       </c>
       <c r="V21" s="22" t="n">
-        <v>-0.1014036215178115</v>
+        <v>-0.09847863851048055</v>
       </c>
     </row>
     <row r="22">
@@ -22806,10 +23704,10 @@
         <v>-0.004895597362709586</v>
       </c>
       <c r="U22" s="22" t="n">
-        <v>0</v>
+        <v>0.1072748518408011</v>
       </c>
       <c r="V22" s="22" t="n">
-        <v>-0.04057170693495321</v>
+        <v>0.06883174582371043</v>
       </c>
     </row>
     <row r="23">
@@ -22876,10 +23774,10 @@
         <v>-0.04578519042151813</v>
       </c>
       <c r="U23" s="22" t="n">
-        <v>-0.01724138869497888</v>
+        <v>0.009298451239764194</v>
       </c>
       <c r="V23" s="22" t="n">
-        <v>-0.142860296397832</v>
+        <v>-0.1194272003308679</v>
       </c>
     </row>
     <row r="24">
@@ -22946,10 +23844,10 @@
         <v>-0.001364955843363505</v>
       </c>
       <c r="U24" s="22" t="n">
-        <v>0</v>
+        <v>0.01086260844466097</v>
       </c>
       <c r="V24" s="22" t="n">
-        <v>-0.08565081531276117</v>
+        <v>-0.07742146844913927</v>
       </c>
     </row>
     <row r="25">
@@ -23016,10 +23914,10 @@
         <v>-0.0002118985753747915</v>
       </c>
       <c r="U25" s="22" t="n">
-        <v>0</v>
+        <v>-0.01315690413355061</v>
       </c>
       <c r="V25" s="22" t="n">
-        <v>0.05403480225293544</v>
+        <v>0.04016287498946647</v>
       </c>
     </row>
     <row r="26">
@@ -23083,13 +23981,13 @@
         <v>0.003613799429639501</v>
       </c>
       <c r="T26" s="22" t="n">
-        <v>-0.008641917294175813</v>
+        <v>-0.01248495741457127</v>
       </c>
       <c r="U26" s="22" t="n">
-        <v>0</v>
+        <v>-0.005672341729736001</v>
       </c>
       <c r="V26" s="22" t="n">
-        <v>0.03895373231664778</v>
+        <v>0.02901177215827485</v>
       </c>
     </row>
     <row r="27">
@@ -23156,10 +24054,10 @@
         <v>0.03136605124068555</v>
       </c>
       <c r="U27" s="22" t="n">
-        <v>0</v>
+        <v>0.00687426257160928</v>
       </c>
       <c r="V27" s="22" t="n">
-        <v>0.04766492453573667</v>
+        <v>0.05553098289544359</v>
       </c>
     </row>
     <row r="28">
@@ -23223,13 +24121,13 @@
         <v>-0.02208176775999497</v>
       </c>
       <c r="T28" s="22" t="n">
-        <v>0.001643007956606694</v>
+        <v>0.002304390359192535</v>
       </c>
       <c r="U28" s="22" t="n">
-        <v>0</v>
+        <v>0.008096843166407833</v>
       </c>
       <c r="V28" s="22" t="n">
-        <v>-0.03864670658035744</v>
+        <v>-0.03067613263742412</v>
       </c>
     </row>
     <row r="29">
@@ -23293,13 +24191,13 @@
         <v>0.003011441046590513</v>
       </c>
       <c r="T29" s="22" t="n">
-        <v>-0.00128260160946847</v>
+        <v>-0.002126740210275313</v>
       </c>
       <c r="U29" s="22" t="n">
-        <v>0</v>
+        <v>-0.00689050830911947</v>
       </c>
       <c r="V29" s="22" t="n">
-        <v>0.1143782653724341</v>
+        <v>0.1057824801600719</v>
       </c>
     </row>
     <row r="30">
@@ -23366,10 +24264,10 @@
         <v>-0.001459248821862547</v>
       </c>
       <c r="U30" s="22" t="n">
-        <v>0</v>
+        <v>-0.01273166073518961</v>
       </c>
       <c r="V30" s="22" t="n">
-        <v>0.1338940967218005</v>
+        <v>0.1194577417727043</v>
       </c>
     </row>
     <row r="31">
@@ -23433,13 +24331,13 @@
         <v>0.0005667618886181872</v>
       </c>
       <c r="T31" s="22" t="n">
-        <v>-0.001494152979594321</v>
+        <v>0.001929961520374168</v>
       </c>
       <c r="U31" s="22" t="n">
-        <v>0</v>
+        <v>-0.00934667478597336</v>
       </c>
       <c r="V31" s="22" t="n">
-        <v>0.1003657791649938</v>
+        <v>0.09388607966581224</v>
       </c>
     </row>
     <row r="32">
@@ -23506,10 +24404,10 @@
         <v>0.0012582410094229</v>
       </c>
       <c r="U32" s="22" t="n">
-        <v>0</v>
+        <v>-0.008521274907279275</v>
       </c>
       <c r="V32" s="22" t="n">
-        <v>0.2420446867712794</v>
+        <v>0.2310527954778671</v>
       </c>
     </row>
     <row r="33">
@@ -23576,10 +24474,10 @@
         <v>-0.01314854918827793</v>
       </c>
       <c r="U33" s="22" t="n">
-        <v>0</v>
+        <v>-0.01343830711524843</v>
       </c>
       <c r="V33" s="22" t="n">
-        <v>0.1103502552875203</v>
+        <v>0.09540541526611557</v>
       </c>
     </row>
     <row r="34">
@@ -23646,10 +24544,10 @@
         <v>-0.003087648914212482</v>
       </c>
       <c r="U34" s="22" t="n">
-        <v>0</v>
+        <v>-0.02927014656500149</v>
       </c>
       <c r="V34" s="22" t="n">
-        <v>0.05735997893544165</v>
+        <v>0.02637989528016804</v>
       </c>
     </row>
     <row r="35">
@@ -23716,10 +24614,10 @@
         <v>0.01971817590603591</v>
       </c>
       <c r="U35" s="22" t="n">
-        <v>-0.003333349890178439</v>
+        <v>0.07345610243579956</v>
       </c>
       <c r="V35" s="22" t="n">
-        <v>-0.08631963521862937</v>
+        <v>-0.01669048419198649</v>
       </c>
     </row>
     <row r="36">
@@ -23786,10 +24684,10 @@
         <v>0.01533788429612737</v>
       </c>
       <c r="U36" s="22" t="n">
-        <v>0</v>
+        <v>0.02943286298765324</v>
       </c>
       <c r="V36" s="22" t="n">
-        <v>0.02198230915507648</v>
+        <v>0.052127850529604</v>
       </c>
     </row>
     <row r="37">
@@ -23856,10 +24754,10 @@
         <v>0.02062888934632923</v>
       </c>
       <c r="U37" s="22" t="n">
-        <v>0.02334384079836682</v>
+        <v>0.07076291590371742</v>
       </c>
       <c r="V37" s="22" t="n">
-        <v>-0.144527972691521</v>
+        <v>-0.1006263472574846</v>
       </c>
     </row>
   </sheetData>
@@ -24382,7 +25280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -24832,14 +25730,524 @@
       </c>
       <c r="E27" s="10" t="inlineStr"/>
     </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>🌐 글로벌 코멘트 (미국장 마감)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n"/>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>① 섹터 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+    </row>
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1D 기준 SOX +3.6%로 나스닥(+1.2%)과 S&amp;P500(+0.6%)을 웃돌았다. 대만 가권과 닛케이225는 0.0%로 보합, TOPIX 전기·정밀은 +2.3%였다.</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="31" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>10.27 OSAT·테스트(+4.5%), 메모리(+4.3%), EDA(+4.1%)로 자금이 들어왔고 기판·PCB(-0.6%)만 밀렸다. 20일 누적 -19.3%인 메모리의 반등이 두드러진다.</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+    </row>
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>국가별 1D 평균은 미국 +4.4%, 일본 +3.0%인 반면 대만은 +0.3%였다. TSMC(ADR) +2.9%와 TSMC(TW) +0.6%의 괴리처럼 온도차가 컸다.</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+    </row>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>국내 반도체 밸류체인에는 메모리 20D -19.3% 이후의 1D 반등과 SOX +3.6%가 업황 바닥 판단의 참고가 될 수 있다.</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+    </row>
+    <row r="38" ht="17.5" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>체크포인트: 메타의 주식 발행이 5D -10.7% 이후 추가 하락으로 이어지는지, 앰코의 4분기 가이던스가 주가에 반영되는지 확인이 필요하다.</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>② 종목 코멘트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>종목</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>등락</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>코멘트</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>Celestica (CA)</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>+12.1%</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 3분기 조정 EPS가 예상을 웃돌고 2026년 조정 EPS 전망이 11.55달러로 상향된 점이 반영된 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>SEC 8-K(셀레스티카 3분기 실적)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="31" customHeight="1">
+      <c r="A43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>Nebius (US)</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>+11.2%</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 실시간 GPU 스팟 가격 공개 소식과 씨티 35억 달러 조달 보도가 겹치며 반등한 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>Credo (US)</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>+10.8%</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 실적 상회에도 투자의견 하향으로 10% 급락한 뒤 낙폭을 되돌린 것으로 보인다. 10.27 직접 뉴스는 미확인.</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Astera Labs (US)</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>+10.5%</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>[추정] Orion 공개 관련 보도 이후 낙폭 축소 성격으로 보인다. Orion 출시는 2027년 1분기 예정이라 매출 시점은 멀다.</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.26·27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Advantest (JP)</t>
+        </is>
+      </c>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>+9.0%</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>특이 뉴스 없음 — 섹터·수급 동반</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="31" customHeight="1">
+      <c r="A47" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Super Micro (US)</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>+7.3%</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 웨드부시가 잠정 1분기 실적을 긍정 평가(10.26)한 뒤 반등이 이어진 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>웨드부시 보도(워치리스트 10.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17.5" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>Dell (US)</t>
+        </is>
+      </c>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>+7.5%</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 AMD AI 청사진 합류 소식과 5D +8.8% 강세가 겹친 수급으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="31" customHeight="1">
+      <c r="A49" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Amkor (US)</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>+8.5%</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 3분기 EPS와 매출이 예상을 소폭 하회했으나 4분기 가이던스 제시 이후 반등한 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>앰코 3분기 실적 공시(SEC 8-K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="31" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B50" s="12" t="inlineStr">
+        <is>
+          <t>AMD (US)</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>+5.5%</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 델·레노버·시스코 등 서버·PC 업체의 AMD AI 청사진 합류 소식 이후 반등으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="31" customHeight="1">
+      <c r="A51" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Lumentum (US)</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>+5.9%</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>[추정] AI 광부품이 완전 매진됐다는 보도(10.27) 이후 수요 재확인 기대로 급등한 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="31" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B52" s="12" t="inlineStr">
+        <is>
+          <t>Cadence (US)</t>
+        </is>
+      </c>
+      <c r="C52" s="17" t="inlineStr">
+        <is>
+          <t>+6.5%</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>3분기 EPS가 예상치를 7센트 웃돌고 백로그 82억 달러, 연간 가이던스 상향이 강세의 근거로 보인다.</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>케이던스 3분기 실적(워치리스트 10.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="31" customHeight="1">
+      <c r="A53" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Broadcom (US)</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 앤스로픽 AI 칩 관련 630억 달러 금융 조달 보도가 부각됐다. 조달 규모와 구조는 보도마다 달라 미확정이다.</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>로이터(워치리스트 10.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="31" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>Intel (US)</t>
+        </is>
+      </c>
+      <c r="C54" s="17" t="inlineStr">
+        <is>
+          <t>+3.6%</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 양자컴퓨팅 소프트웨어 확보를 위한 클래식 인수(23억 달러) 발표가 사업 확대 기대로 작용한 것으로 보인다.</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="31" customHeight="1">
+      <c r="A55" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Lam Research (US)</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>+1.4%</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>[추정] 매출 54.4% 성장 발표에도 5D -8.6%로 그룹 내 낙폭이 컸다. 1D 반등은 제한적이었다.</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>워치리스트 뉴스(10.27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="31" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B56" s="12" t="inlineStr">
+        <is>
+          <t>Meta (US)</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>-1.6%</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>[추정] 10.26 약 350억 달러 규모 주식 발행 발표 이후 희석 우려로 5D -10.7%를 기록했다. 1D 낙폭은 둔화됐다.</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>메타 발행설명서(FWP, 10.26)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="14">
+    <mergeCell ref="A30:E30"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B36:E36"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25016,22 +26424,22 @@
         </is>
       </c>
       <c r="L5" s="21" t="n">
-        <v>4.986000061035156</v>
+        <v>4.993000030517578</v>
       </c>
       <c r="M5" s="21" t="n">
-        <v>0</v>
+        <v>0.006999969482421875</v>
       </c>
       <c r="N5" s="21" t="n">
-        <v>-0.1310000419616699</v>
+        <v>-0.124000072479248</v>
       </c>
       <c r="O5" s="21" t="n">
-        <v>-0.1979999542236328</v>
+        <v>-0.1909999847412109</v>
       </c>
       <c r="P5" s="21" t="n">
-        <v>0.3450002670288086</v>
+        <v>0.3520002365112305</v>
       </c>
       <c r="Q5" s="21" t="n">
-        <v>0.8229999542236328</v>
+        <v>0.8299999237060547</v>
       </c>
     </row>
     <row r="6">
@@ -25074,22 +26482,22 @@
         </is>
       </c>
       <c r="L6" s="21" t="n">
-        <v>1323.969970703125</v>
+        <v>1326.81005859375</v>
       </c>
       <c r="M6" s="21" t="n">
-        <v>2.2099609375</v>
+        <v>5.050048828125</v>
       </c>
       <c r="N6" s="21" t="n">
-        <v>-6.030029296875</v>
+        <v>-3.18994140625</v>
       </c>
       <c r="O6" s="21" t="n">
-        <v>-43.3900146484375</v>
+        <v>-40.5499267578125</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>-134.0400390625</v>
+        <v>-131.199951171875</v>
       </c>
       <c r="Q6" s="21" t="n">
-        <v>-113.9400634765625</v>
+        <v>-111.0999755859375</v>
       </c>
     </row>
     <row r="7">
@@ -25132,22 +26540,22 @@
         </is>
       </c>
       <c r="L7" s="21" t="n">
-        <v>157.8569946289062</v>
+        <v>157.9080047607422</v>
       </c>
       <c r="M7" s="21" t="n">
-        <v>1.026992797851562</v>
+        <v>1.0780029296875</v>
       </c>
       <c r="N7" s="21" t="n">
-        <v>-0.6660003662109375</v>
+        <v>-0.614990234375</v>
       </c>
       <c r="O7" s="21" t="n">
-        <v>-0.954010009765625</v>
+        <v>-0.9029998779296875</v>
       </c>
       <c r="P7" s="21" t="n">
-        <v>-5.753997802734375</v>
+        <v>-5.702987670898438</v>
       </c>
       <c r="Q7" s="21" t="n">
-        <v>1.444000244140625</v>
+        <v>1.495010375976562</v>
       </c>
     </row>
     <row r="8">
@@ -25280,22 +26688,22 @@
         </is>
       </c>
       <c r="C11" s="21" t="n">
-        <v>26169.380859375</v>
+        <v>26477.810546875</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>0</v>
+        <v>0.0117858992980151</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-0.009666648632012387</v>
+        <v>0.002005320518676745</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-0.03322432018910204</v>
+        <v>-0.02182999938308061</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0.04962685734093997</v>
+        <v>0.06199765378205235</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>0.1259526656486749</v>
+        <v>0.1392230303803419</v>
       </c>
     </row>
     <row r="12">
@@ -25310,22 +26718,22 @@
         </is>
       </c>
       <c r="C12" s="21" t="n">
-        <v>7676.77001953125</v>
+        <v>7722.60009765625</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0</v>
+        <v>0.005969968881235133</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.004641747887336178</v>
+        <v>0.001300509903457092</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-0.008606045059483591</v>
+        <v>-0.002687453999444034</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0.03555691855583709</v>
+        <v>0.04173916113436316</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>0.1214330610665766</v>
+        <v>0.1281279815435323</v>
       </c>
     </row>
     <row r="13">
@@ -25340,22 +26748,22 @@
         </is>
       </c>
       <c r="C13" s="21" t="n">
-        <v>11083.4697265625</v>
+        <v>11482.5048828125</v>
       </c>
       <c r="D13" s="22" t="n">
-        <v>0</v>
+        <v>0.03600272893728196</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.01775462821324902</v>
+        <v>0.01760888565708907</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.1251455332096301</v>
+        <v>-0.09364838498220607</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>-0.04079749517355058</v>
+        <v>-0.006263587396322046</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.5647700818612666</v>
+        <v>0.6211060749676864</v>
       </c>
     </row>
     <row r="14">
@@ -25370,22 +26778,22 @@
         </is>
       </c>
       <c r="C14" s="21" t="n">
-        <v>541.6199951171875</v>
+        <v>557.97998046875</v>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0</v>
+        <v>0.03020565248523144</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.008675580865104893</v>
+        <v>0.02126802003940775</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.1070627847249901</v>
+        <v>-0.08009103350926294</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.01263329291768522</v>
+        <v>0.01719076271193032</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>0.5039568705013415</v>
+        <v>0.5493848690844811</v>
       </c>
     </row>
     <row r="15">
@@ -25400,22 +26808,22 @@
         </is>
       </c>
       <c r="C15" s="21" t="n">
-        <v>46096.23046875</v>
+        <v>46041.4296875</v>
       </c>
       <c r="D15" s="22" t="n">
-        <v>0.001190249338953064</v>
+        <v>0</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.004249012107849226</v>
+        <v>-0.005432795066066198</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.04015381764782344</v>
+        <v>-0.04129491574061406</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.05642453734452268</v>
+        <v>0.05516862358781327</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>0.5915228455868267</v>
+        <v>0.5896307885915262</v>
       </c>
     </row>
     <row r="16">
@@ -25430,22 +26838,22 @@
         </is>
       </c>
       <c r="C16" s="21" t="n">
-        <v>63268.37109375</v>
+        <v>62189.6484375</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>0.01734569471532077</v>
+        <v>0</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.01259532528438778</v>
+        <v>-0.02943052706198046</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.04664912536384802</v>
+        <v>-0.06290371150297758</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>-0.02560896044701166</v>
+        <v>-0.04222228037673292</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>0.2568340098985737</v>
+        <v>0.2354050510335801</v>
       </c>
     </row>
     <row r="17">
@@ -25490,22 +26898,22 @@
         </is>
       </c>
       <c r="C18" s="21" t="n">
-        <v>3.723999977111816</v>
+        <v>3.778000116348267</v>
       </c>
       <c r="D18" s="22" t="n">
-        <v>-0.0194839700546775</v>
+        <v>0</v>
       </c>
       <c r="E18" s="22" t="n">
-        <v>-0.0638511697464198</v>
+        <v>-0.05027647385747425</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>-0.121698071193591</v>
+        <v>-0.1089621886106988</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>-0.1932409368403589</v>
+        <v>-0.1815424669132254</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>-0.3090908962229807</v>
+        <v>-0.2990723172667517</v>
       </c>
     </row>
     <row r="20">
@@ -25990,16 +27398,16 @@
         </is>
       </c>
       <c r="J31" s="22" t="n">
-        <v>0</v>
+        <v>0.0117858992980151</v>
       </c>
       <c r="K31" s="22" t="n">
-        <v>0</v>
+        <v>0.005969968881235133</v>
       </c>
       <c r="L31" s="22" t="n">
-        <v>0</v>
+        <v>0.03600272893728196</v>
       </c>
       <c r="M31" s="22" t="n">
-        <v>0</v>
+        <v>0.03020565248523144</v>
       </c>
     </row>
     <row r="33">
@@ -26370,7 +27778,7 @@
         <v>-0.0195729537366548</v>
       </c>
       <c r="E43" s="22" t="n">
-        <v>0</v>
+        <v>-0.005265924279692524</v>
       </c>
       <c r="I43" s="20" t="inlineStr">
         <is>
@@ -26397,16 +27805,16 @@
         </is>
       </c>
       <c r="B44" s="22" t="n">
-        <v>0.001190249338953064</v>
+        <v>0</v>
       </c>
       <c r="C44" s="22" t="n">
-        <v>0.01734569471532077</v>
+        <v>0</v>
       </c>
       <c r="D44" s="22" t="n">
         <v>0.02309849859759106</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>-0.0194839700546775</v>
+        <v>0</v>
       </c>
       <c r="I44" s="20" t="inlineStr">
         <is>
@@ -26414,13 +27822,13 @@
         </is>
       </c>
       <c r="J44" s="21" t="n">
-        <v>4.986000061035156</v>
+        <v>4.993000030517578</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>1323.969970703125</v>
+        <v>1326.81005859375</v>
       </c>
       <c r="L44" s="23" t="n">
-        <v>157.8569946289062</v>
+        <v>157.9080047607422</v>
       </c>
       <c r="M44" s="21" t="n">
         <v>61.333</v>
@@ -30962,27 +32370,27 @@
     <row r="5">
       <c r="A5" s="20" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Flex Ltd.</t>
         </is>
       </c>
       <c r="B5" s="22" t="n">
-        <v>0</v>
+        <v>0.08260814114588366</v>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
-          <t>Teledyne Technologies</t>
+          <t>Fair Isaac</t>
         </is>
       </c>
       <c r="F5" s="22" t="n">
-        <v>0</v>
+        <v>-0.02306271543904892</v>
       </c>
       <c r="I5" s="20" t="inlineStr">
         <is>
-          <t>Advantest (JP)</t>
+          <t>Celestica (CA)</t>
         </is>
       </c>
       <c r="J5" s="22" t="n">
-        <v>0.08979723205664625</v>
+        <v>0.1211839261629251</v>
       </c>
       <c r="M5" s="20" t="inlineStr">
         <is>
@@ -30996,27 +32404,27 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>Adobe Inc.</t>
+          <t>Dell Technologies</t>
         </is>
       </c>
       <c r="B6" s="22" t="n">
-        <v>0</v>
+        <v>0.07465369712598746</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0</v>
+        <v>-0.02713945803537221</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>Ibiden (JP)</t>
+          <t>Nebius (US)</t>
         </is>
       </c>
       <c r="J6" s="22" t="n">
-        <v>0.08535402521823476</v>
+        <v>0.1122202418528453</v>
       </c>
       <c r="M6" s="20" t="inlineStr">
         <is>
@@ -31030,27 +32438,27 @@
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Supermicro</t>
         </is>
       </c>
       <c r="B7" s="22" t="n">
-        <v>0</v>
+        <v>0.07341699684006753</v>
       </c>
       <c r="E7" s="20" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Autodesk</t>
         </is>
       </c>
       <c r="F7" s="22" t="n">
-        <v>0</v>
+        <v>-0.02946478626837423</v>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>Nanya (TW)</t>
+          <t>Credo (US)</t>
         </is>
       </c>
       <c r="J7" s="22" t="n">
-        <v>0.06521739130434789</v>
+        <v>0.1077075715295517</v>
       </c>
       <c r="M7" s="20" t="inlineStr">
         <is>
@@ -31064,27 +32472,27 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>Akamai Technologies</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>0</v>
+        <v>0.06949709280503957</v>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Trimble Inc.</t>
+          <t>GoDaddy</t>
         </is>
       </c>
       <c r="F8" s="22" t="n">
-        <v>0</v>
+        <v>-0.03287197796743124</v>
       </c>
       <c r="I8" s="20" t="inlineStr">
         <is>
-          <t>Wiwynn (TW)</t>
+          <t>Astera Labs (US)</t>
         </is>
       </c>
       <c r="J8" s="22" t="n">
-        <v>0.05978260869565211</v>
+        <v>0.1047358161649667</v>
       </c>
       <c r="M8" s="20" t="inlineStr">
         <is>
@@ -31098,27 +32506,27 @@
     <row r="9">
       <c r="A9" s="20" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Cadence Design Systems</t>
         </is>
       </c>
       <c r="B9" s="22" t="n">
-        <v>0</v>
+        <v>0.06490353624801748</v>
       </c>
       <c r="E9" s="20" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="F9" s="22" t="n">
-        <v>0</v>
+        <v>-0.03365795389205273</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>Towa (JP)</t>
+          <t>Advantest (JP)</t>
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.05830753353973162</v>
+        <v>0.08979723205664625</v>
       </c>
       <c r="M9" s="20" t="inlineStr">
         <is>
@@ -31132,27 +32540,27 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Coherent Corp.</t>
         </is>
       </c>
       <c r="B10" s="22" t="n">
-        <v>0</v>
+        <v>0.06451464237531734</v>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="F10" s="22" t="n">
-        <v>0</v>
+        <v>-0.03447751393257981</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>Winbond (TW)</t>
+          <t>Ibiden (JP)</t>
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.05501618122977336</v>
+        <v>0.08535402521823476</v>
       </c>
       <c r="M10" s="20" t="inlineStr">
         <is>
@@ -31166,27 +32574,27 @@
     <row r="11">
       <c r="A11" s="20" t="inlineStr">
         <is>
-          <t>Apple Inc.</t>
+          <t>ON Semiconductor</t>
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>0</v>
+        <v>0.0622468371904048</v>
       </c>
       <c r="E11" s="20" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Adobe Inc.</t>
         </is>
       </c>
       <c r="F11" s="22" t="n">
-        <v>0</v>
+        <v>-0.0396720853010103</v>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>SUMCO (JP)</t>
+          <t>Amkor (US)</t>
         </is>
       </c>
       <c r="J11" s="22" t="n">
-        <v>0.05496688741721845</v>
+        <v>0.08503116372304897</v>
       </c>
       <c r="M11" s="20" t="inlineStr">
         <is>
@@ -31200,27 +32608,27 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>Lumentum</t>
         </is>
       </c>
       <c r="B12" s="22" t="n">
-        <v>0</v>
+        <v>0.05877034412011573</v>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>Gartner</t>
         </is>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0</v>
+        <v>-0.04371729280561598</v>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>SoftBank G (JP)</t>
+          <t>CoreWeave (US)</t>
         </is>
       </c>
       <c r="J12" s="22" t="n">
-        <v>0.04949566033309871</v>
+        <v>0.07936222462588627</v>
       </c>
       <c r="M12" s="20" t="inlineStr">
         <is>
@@ -31234,27 +32642,27 @@
     <row r="13">
       <c r="A13" s="20" t="inlineStr">
         <is>
-          <t>Arista Networks</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="B13" s="22" t="n">
-        <v>0</v>
+        <v>0.05634656052166864</v>
       </c>
       <c r="E13" s="20" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="F13" s="22" t="n">
-        <v>0</v>
+        <v>-0.0449956054509133</v>
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>Lasertec (JP)</t>
+          <t>Silicon Motion (US)</t>
         </is>
       </c>
       <c r="J13" s="22" t="n">
-        <v>0.04896221394358702</v>
+        <v>0.07923673788725694</v>
       </c>
       <c r="M13" s="20" t="inlineStr">
         <is>
@@ -31268,27 +32676,27 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="B14" s="22" t="n">
-        <v>0</v>
+        <v>0.05625818915972625</v>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0</v>
+        <v>-0.04882090472036205</v>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>Ulvac (JP)</t>
+          <t>Dell (US)</t>
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0.04817942683095677</v>
+        <v>0.07465369712598746</v>
       </c>
       <c r="M14" s="20" t="inlineStr">
         <is>
@@ -31306,7 +32714,7 @@
         </is>
       </c>
       <c r="B15" s="28" t="n">
-        <v>0</v>
+        <v>0.06632160375322285</v>
       </c>
       <c r="E15" s="26" t="inlineStr">
         <is>
@@ -31314,7 +32722,7 @@
         </is>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0</v>
+        <v>-0.03578802938127608</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
@@ -31322,7 +32730,7 @@
         </is>
       </c>
       <c r="J15" s="28" t="n">
-        <v>0.0615079160569247</v>
+        <v>0.09392826363473494</v>
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
@@ -31360,53 +32768,53 @@
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>JP (32종목)</t>
+          <t>CA (1종목)</t>
         </is>
       </c>
       <c r="B19" s="22" t="n">
-        <v>0.02957615762842359</v>
+        <v>0.1211839261629251</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>0.02868534635184694</v>
+        <v>0.1211839261629251</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>TW (39종목)</t>
+          <t>US (49종목)</t>
         </is>
       </c>
       <c r="B20" s="22" t="n">
-        <v>0.002112507105059192</v>
+        <v>0.04385008217869053</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>0.002631578947368318</v>
+        <v>0.03923287364383454</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>CA (1종목)</t>
+          <t>IL (2종목)</t>
         </is>
       </c>
       <c r="B21" s="22" t="n">
-        <v>0</v>
+        <v>0.04048014322885696</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>0</v>
+        <v>0.04048014322885696</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>IL (2종목)</t>
+          <t>JP (32종목)</t>
         </is>
       </c>
       <c r="B22" s="22" t="n">
-        <v>0</v>
+        <v>0.02957615762842359</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>0</v>
+        <v>0.02868534635184694</v>
       </c>
     </row>
     <row r="23">
@@ -31416,23 +32824,23 @@
         </is>
       </c>
       <c r="B23" s="22" t="n">
-        <v>0</v>
+        <v>0.02807839662423306</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>0</v>
+        <v>0.02807839662423306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>US (49종목)</t>
+          <t>TW (39종목)</t>
         </is>
       </c>
       <c r="B24" s="22" t="n">
-        <v>0</v>
+        <v>0.00286777449955138</v>
       </c>
       <c r="C24" s="22" t="n">
-        <v>0</v>
+        <v>0.003105590062111752</v>
       </c>
     </row>
     <row r="26">
@@ -31546,13 +32954,13 @@
         </is>
       </c>
       <c r="B28" s="31" t="n">
-        <v>0</v>
+        <v>-0.002384450909327596</v>
       </c>
       <c r="C28" s="31" t="n">
-        <v>0.001372479131087623</v>
+        <v>-0.001015244387352121</v>
       </c>
       <c r="D28" s="31" t="n">
-        <v>0.06394450444918731</v>
+        <v>0.06140758100807919</v>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
@@ -31584,17 +32992,17 @@
       </c>
       <c r="P28" s="29" t="inlineStr">
         <is>
-          <t>Sony (JP)</t>
+          <t>Texas Instruments (US)</t>
         </is>
       </c>
       <c r="Q28" s="31" t="n">
-        <v>-0.01571946795646917</v>
+        <v>0.03619350839141289</v>
       </c>
       <c r="R28" s="31" t="n">
-        <v>0.02777777777777768</v>
+        <v>0.1120671215336353</v>
       </c>
       <c r="S28" s="31" t="n">
-        <v>0.1008926156342982</v>
+        <v>0.1331157259001579</v>
       </c>
     </row>
     <row r="29">
@@ -31604,13 +33012,13 @@
         </is>
       </c>
       <c r="B29" s="22" t="n">
-        <v>0</v>
+        <v>0.009275689591572434</v>
       </c>
       <c r="C29" s="22" t="n">
-        <v>0.01298970150842238</v>
+        <v>0.02238587953907412</v>
       </c>
       <c r="D29" s="22" t="n">
-        <v>0.02044393470132722</v>
+        <v>0.02990925588521942</v>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
@@ -31628,31 +33036,31 @@
       </c>
       <c r="K29" s="20" t="inlineStr">
         <is>
-          <t>Macronix (TW)</t>
+          <t>Micron (US)</t>
         </is>
       </c>
       <c r="L29" s="22" t="n">
-        <v>0.03517587939698497</v>
+        <v>0.02773043844205758</v>
       </c>
       <c r="M29" s="22" t="n">
-        <v>0.03000000000000003</v>
+        <v>0.03648152730725007</v>
       </c>
       <c r="N29" s="22" t="n">
-        <v>-0.134453781512605</v>
+        <v>-0.1335224040612967</v>
       </c>
       <c r="P29" s="20" t="inlineStr">
         <is>
-          <t>Texas Instruments (US)</t>
+          <t>Analog Devices (US)</t>
         </is>
       </c>
       <c r="Q29" s="22" t="n">
-        <v>0</v>
+        <v>0.04270343867943938</v>
       </c>
       <c r="R29" s="22" t="n">
-        <v>0.07322340135097805</v>
+        <v>0.07127570628538393</v>
       </c>
       <c r="S29" s="22" t="n">
-        <v>0.09353679281315608</v>
+        <v>0.1041455597253853</v>
       </c>
     </row>
     <row r="30">
@@ -31662,13 +33070,13 @@
         </is>
       </c>
       <c r="B30" s="22" t="n">
-        <v>0</v>
+        <v>0.01609863834188441</v>
       </c>
       <c r="C30" s="22" t="n">
-        <v>-0.05155545175031895</v>
+        <v>-0.03628678598071544</v>
       </c>
       <c r="D30" s="22" t="n">
-        <v>-0.000722140375837399</v>
+        <v>0.01536487248930429</v>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
@@ -31676,41 +33084,41 @@
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>0</v>
+        <v>0.00898149278428817</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>-0.00217120717906738</v>
+        <v>0.00679078492360885</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>-0.04217105555624345</v>
+        <v>-0.03356832180313951</v>
       </c>
       <c r="K30" s="20" t="inlineStr">
         <is>
-          <t>Phison (TW)</t>
+          <t>Macronix (TW)</t>
         </is>
       </c>
       <c r="L30" s="22" t="n">
-        <v>0.01595744680851063</v>
+        <v>0.03517587939698497</v>
       </c>
       <c r="M30" s="22" t="n">
-        <v>0.03523035230352312</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="N30" s="22" t="n">
-        <v>-0.1376975169300225</v>
+        <v>-0.134453781512605</v>
       </c>
       <c r="P30" s="20" t="inlineStr">
         <is>
-          <t>Analog Devices (US)</t>
+          <t>Sony (JP)</t>
         </is>
       </c>
       <c r="Q30" s="22" t="n">
-        <v>0</v>
+        <v>-0.01571946795646917</v>
       </c>
       <c r="R30" s="22" t="n">
-        <v>0.02740210355701</v>
+        <v>0.02777777777777768</v>
       </c>
       <c r="S30" s="22" t="n">
-        <v>0.05892578730128784</v>
+        <v>0.1008926156342982</v>
       </c>
     </row>
     <row r="31">
@@ -31720,41 +33128,41 @@
         </is>
       </c>
       <c r="B31" s="22" t="n">
-        <v>0</v>
+        <v>0.01193181478834893</v>
       </c>
       <c r="C31" s="22" t="n">
-        <v>-0.06900203088797208</v>
+        <v>-0.05789353555219845</v>
       </c>
       <c r="D31" s="22" t="n">
-        <v>-0.06225024306656191</v>
+        <v>-0.05106118664901294</v>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>Socionext (JP)</t>
+          <t>Broadcom (US)</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>0.03979143798024154</v>
+        <v>0.03997925876507691</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>0.03893611187277224</v>
+        <v>0.02380593824600918</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>-0.05274999999999996</v>
+        <v>-0.03566298771903642</v>
       </c>
       <c r="K31" s="20" t="inlineStr">
         <is>
-          <t>Nanya (TW)</t>
+          <t>Phison (TW)</t>
         </is>
       </c>
       <c r="L31" s="22" t="n">
-        <v>0.06521739130434789</v>
+        <v>0.01595744680851063</v>
       </c>
       <c r="M31" s="22" t="n">
-        <v>0.04502369668246442</v>
+        <v>0.03523035230352312</v>
       </c>
       <c r="N31" s="22" t="n">
-        <v>-0.1436893203883495</v>
+        <v>-0.1376975169300225</v>
       </c>
       <c r="P31" s="20" t="inlineStr">
         <is>
@@ -31762,13 +33170,13 @@
         </is>
       </c>
       <c r="Q31" s="22" t="n">
-        <v>0</v>
+        <v>0.03777779473198795</v>
       </c>
       <c r="R31" s="22" t="n">
-        <v>-0.04275682606464826</v>
+        <v>-0.006594289931121988</v>
       </c>
       <c r="S31" s="22" t="n">
-        <v>-0.03059022457901095</v>
+        <v>0.006031938928025671</v>
       </c>
     </row>
     <row r="32">
@@ -31778,55 +33186,55 @@
         </is>
       </c>
       <c r="B32" s="22" t="n">
-        <v>0</v>
+        <v>0.03545931546306291</v>
       </c>
       <c r="C32" s="22" t="n">
-        <v>-0.03873724153346059</v>
+        <v>-0.004651522138101494</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>-0.1279745456034717</v>
+        <v>-0.09705311992420429</v>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>Alchip (TW)</t>
+          <t>Socionext (JP)</t>
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>0</v>
+        <v>0.03979143798024154</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>-0.0398351648351648</v>
+        <v>0.03893611187277224</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>-0.07047872340425532</v>
+        <v>-0.05274999999999996</v>
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
-          <t>Micron (US)</t>
+          <t>Nanya (TW)</t>
         </is>
       </c>
       <c r="L32" s="22" t="n">
-        <v>0</v>
+        <v>0.06521739130434789</v>
       </c>
       <c r="M32" s="22" t="n">
-        <v>0.00851496514831096</v>
+        <v>0.04502369668246442</v>
       </c>
       <c r="N32" s="22" t="n">
-        <v>-0.1569018844550312</v>
+        <v>-0.1436893203883495</v>
       </c>
       <c r="P32" s="20" t="inlineStr">
         <is>
-          <t>TSMC (TW)</t>
+          <t>TSMC(ADR) (TW)</t>
         </is>
       </c>
       <c r="Q32" s="22" t="n">
-        <v>0.006289308176100628</v>
+        <v>0.02945542838519533</v>
       </c>
       <c r="R32" s="22" t="n">
-        <v>-0.002079002079002024</v>
+        <v>0.02773597656288973</v>
       </c>
       <c r="S32" s="22" t="n">
-        <v>-0.04000000000000004</v>
+        <v>-0.02172114572842065</v>
       </c>
     </row>
     <row r="33">
@@ -31836,27 +33244,27 @@
         </is>
       </c>
       <c r="B33" s="22" t="n">
-        <v>0</v>
+        <v>-0.01644569138121366</v>
       </c>
       <c r="C33" s="22" t="n">
-        <v>-0.09173929051696972</v>
+        <v>-0.1066762658388098</v>
       </c>
       <c r="D33" s="22" t="n">
-        <v>-0.1525869933511788</v>
+        <v>-0.1665232861309517</v>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>Broadcom (US)</t>
+          <t>Qualcomm (US)</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>0</v>
+        <v>0.02544538925458428</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>-0.01555157988273048</v>
+        <v>0.048147465322534</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>-0.07273437988939779</v>
+        <v>-0.06626448468980461</v>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
@@ -31864,71 +33272,71 @@
         </is>
       </c>
       <c r="L33" s="22" t="n">
-        <v>0</v>
+        <v>0.06949709280503957</v>
       </c>
       <c r="M33" s="22" t="n">
-        <v>-0.02248024340348054</v>
+        <v>0.04545453783946751</v>
       </c>
       <c r="N33" s="22" t="n">
-        <v>-0.2481791824878877</v>
+        <v>-0.1959298213604878</v>
       </c>
       <c r="P33" s="20" t="inlineStr">
         <is>
-          <t>TSMC(ADR) (TW)</t>
+          <t>TSMC (TW)</t>
         </is>
       </c>
       <c r="Q33" s="22" t="n">
-        <v>0</v>
+        <v>0.006289308176100628</v>
       </c>
       <c r="R33" s="22" t="n">
-        <v>-0.001670253781654862</v>
+        <v>-0.002079002079002024</v>
       </c>
       <c r="S33" s="22" t="n">
-        <v>-0.04971227767858932</v>
+        <v>-0.04000000000000004</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="20" t="inlineStr">
         <is>
-          <t>SoftBank G (JP)</t>
+          <t>Nebius (US)</t>
         </is>
       </c>
       <c r="B34" s="22" t="n">
-        <v>0.04949566033309871</v>
+        <v>0.1122202418528453</v>
       </c>
       <c r="C34" s="22" t="n">
-        <v>-0.01756697408871322</v>
+        <v>-0.005715927354812966</v>
       </c>
       <c r="D34" s="22" t="n">
-        <v>-0.2915281076801267</v>
+        <v>-0.2477384018288731</v>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>Qualcomm (US)</t>
+          <t>Marvell (US)</t>
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0</v>
+        <v>0.04187701512550812</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>0.02213874703210883</v>
+        <v>0.01310210955521218</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>-0.08943418626227839</v>
+        <v>-0.06642386729660688</v>
       </c>
       <c r="K34" s="20" t="inlineStr">
         <is>
-          <t>Seagate (US)</t>
+          <t>Silicon Motion (US)</t>
         </is>
       </c>
       <c r="L34" s="22" t="n">
-        <v>0</v>
+        <v>0.07923673788725694</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>-0.04579856129416626</v>
+        <v>-0.04459522187829057</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>-0.3026973435509162</v>
+        <v>-0.2616714314171146</v>
       </c>
       <c r="P34" s="20" t="inlineStr">
         <is>
@@ -31948,45 +33356,45 @@
     <row r="35">
       <c r="A35" s="20" t="inlineStr">
         <is>
-          <t>Nebius (US)</t>
+          <t>SoftBank G (JP)</t>
         </is>
       </c>
       <c r="B35" s="22" t="n">
-        <v>0</v>
+        <v>0.04949566033309871</v>
       </c>
       <c r="C35" s="22" t="n">
-        <v>-0.1060367045749757</v>
+        <v>-0.01756697408871322</v>
       </c>
       <c r="D35" s="22" t="n">
-        <v>-0.323639716430681</v>
+        <v>-0.2915281076801267</v>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>Marvell (US)</t>
+          <t>Alchip (TW)</t>
         </is>
       </c>
       <c r="G35" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="22" t="n">
-        <v>-0.02761833225280386</v>
+        <v>-0.0398351648351648</v>
       </c>
       <c r="I35" s="22" t="n">
-        <v>-0.1039478564646794</v>
+        <v>-0.07047872340425532</v>
       </c>
       <c r="K35" s="20" t="inlineStr">
         <is>
-          <t>Kioxia (JP)</t>
+          <t>Seagate (US)</t>
         </is>
       </c>
       <c r="L35" s="22" t="n">
-        <v>0.004382470119521864</v>
+        <v>0.03669603515464193</v>
       </c>
       <c r="M35" s="22" t="n">
-        <v>-0.04071537290715377</v>
+        <v>-0.01078315175480704</v>
       </c>
       <c r="N35" s="22" t="n">
-        <v>-0.3070368334249588</v>
+        <v>-0.2771091007564354</v>
       </c>
       <c r="P35" s="20" t="inlineStr">
         <is>
@@ -32010,27 +33418,27 @@
         </is>
       </c>
       <c r="B36" s="31" t="n">
-        <v>0</v>
+        <v>0.07936222462588627</v>
       </c>
       <c r="C36" s="31" t="n">
-        <v>-0.1117013089022434</v>
+        <v>-0.04120394864446242</v>
       </c>
       <c r="D36" s="31" t="n">
-        <v>-0.3649022133759877</v>
+        <v>-0.3144994401745297</v>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>GUC (TW)</t>
+          <t>AMD (US)</t>
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>-0.02043506921555704</v>
+        <v>0.05454746813484346</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>-0.04067140090380894</v>
+        <v>0.0477241650097362</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>-0.1138938580799046</v>
+        <v>-0.08843002372447439</v>
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
@@ -32038,13 +33446,13 @@
         </is>
       </c>
       <c r="L36" s="22" t="n">
-        <v>0</v>
+        <v>0.03923287364383454</v>
       </c>
       <c r="M36" s="22" t="n">
-        <v>-0.08041720871512903</v>
+        <v>-0.04433933325960493</v>
       </c>
       <c r="N36" s="22" t="n">
-        <v>-0.3088182711490853</v>
+        <v>-0.2817012257161502</v>
       </c>
       <c r="P36" s="20" t="inlineStr">
         <is>
@@ -32068,41 +33476,41 @@
         </is>
       </c>
       <c r="B37" s="28" t="n">
-        <v>0.005499517814788746</v>
+        <v>0.0327792714117953</v>
       </c>
       <c r="C37" s="28" t="n">
-        <v>-0.05244186906834929</v>
+        <v>-0.02762492493845465</v>
       </c>
       <c r="D37" s="28" t="n">
-        <v>-0.1376906134148145</v>
+        <v>-0.1179690925561217</v>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>AMD (US)</t>
+          <t>Monolithic Power (US)</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>0</v>
+        <v>0.03822594118806033</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>-0.006470361298363869</v>
+        <v>-0.02950972650361039</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>-0.1355818454641963</v>
+        <v>-0.1059263275159155</v>
       </c>
       <c r="K37" s="29" t="inlineStr">
         <is>
-          <t>Silicon Motion (US)</t>
+          <t>Kioxia (JP)</t>
         </is>
       </c>
       <c r="L37" s="31" t="n">
-        <v>0</v>
+        <v>0.004382470119521864</v>
       </c>
       <c r="M37" s="31" t="n">
-        <v>-0.1147403117577004</v>
+        <v>-0.04071537290715377</v>
       </c>
       <c r="N37" s="31" t="n">
-        <v>-0.3158789516114348</v>
+        <v>-0.3070368334249588</v>
       </c>
       <c r="P37" s="20" t="inlineStr">
         <is>
@@ -32122,17 +33530,17 @@
     <row r="38">
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>Monolithic Power (US)</t>
+          <t>GUC (TW)</t>
         </is>
       </c>
       <c r="G38" s="22" t="n">
-        <v>0</v>
+        <v>-0.02043506921555704</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>-0.06524174074687394</v>
+        <v>-0.04067140090380894</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>-0.1388447957089376</v>
+        <v>-0.1138938580799046</v>
       </c>
       <c r="K38" s="26" t="inlineStr">
         <is>
@@ -32140,13 +33548,13 @@
         </is>
       </c>
       <c r="L38" s="28" t="n">
-        <v>0.01757493688591387</v>
+        <v>0.04281425467919693</v>
       </c>
       <c r="M38" s="28" t="n">
-        <v>-0.0116530224926938</v>
+        <v>0.01206094933492423</v>
       </c>
       <c r="N38" s="28" t="n">
-        <v>-0.2110425549278407</v>
+        <v>-0.1927883899335536</v>
       </c>
       <c r="P38" s="29" t="inlineStr">
         <is>
@@ -32154,13 +33562,13 @@
         </is>
       </c>
       <c r="Q38" s="31" t="n">
-        <v>0</v>
+        <v>0.03614454072006912</v>
       </c>
       <c r="R38" s="31" t="n">
-        <v>-0.01330571696170213</v>
+        <v>0.02235789472983507</v>
       </c>
       <c r="S38" s="31" t="n">
-        <v>-0.2620717589992475</v>
+        <v>-0.2353996816439068</v>
       </c>
     </row>
     <row r="39">
@@ -32175,13 +33583,13 @@
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>0</v>
+        <v>0.1077075715295517</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>-0.1187102866447824</v>
+        <v>-0.02378871180531739</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>-0.2203538572066317</v>
+        <v>-0.136380064513976</v>
       </c>
       <c r="P39" s="26" t="inlineStr">
         <is>
@@ -32189,13 +33597,13 @@
         </is>
       </c>
       <c r="Q39" s="28" t="n">
-        <v>0.004657911095002667</v>
+        <v>0.02122833935937582</v>
       </c>
       <c r="R39" s="28" t="n">
-        <v>0.00924448630869399</v>
+        <v>0.02596718640693392</v>
       </c>
       <c r="S39" s="28" t="n">
-        <v>-0.05534273633805513</v>
+        <v>-0.03933509285408738</v>
       </c>
     </row>
     <row r="40">
@@ -32221,17 +33629,17 @@
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>MediaTek (TW)</t>
+          <t>Astera Labs (US)</t>
         </is>
       </c>
       <c r="G40" s="22" t="n">
-        <v>-0.01246882793017456</v>
+        <v>0.1047358161649667</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>-0.04578313253012045</v>
+        <v>0.006636287673619679</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>-0.23625843780135</v>
+        <v>-0.204655137220313</v>
       </c>
       <c r="K40" s="19" t="inlineStr">
         <is>
@@ -32256,17 +33664,17 @@
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>Astera Labs (US)</t>
+          <t>MediaTek (TW)</t>
         </is>
       </c>
       <c r="G41" s="22" t="n">
-        <v>0</v>
+        <v>-0.01246882793017456</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>-0.08879908395827574</v>
+        <v>-0.04578313253012045</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>-0.2800587695792416</v>
+        <v>-0.23625843780135</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -32315,13 +33723,13 @@
         </is>
       </c>
       <c r="G42" s="31" t="n">
-        <v>0</v>
+        <v>0.01455115250139616</v>
       </c>
       <c r="H42" s="31" t="n">
-        <v>0.01035921727229239</v>
+        <v>0.02506110832401265</v>
       </c>
       <c r="I42" s="31" t="n">
-        <v>-0.3283918458528267</v>
+        <v>-0.31861917318065</v>
       </c>
       <c r="K42" s="29" t="inlineStr">
         <is>
@@ -32379,13 +33787,13 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>0.004102257815514558</v>
+        <v>0.03317233151206628</v>
       </c>
       <c r="H43" s="28" t="n">
-        <v>-0.020019529709901</v>
+        <v>0.007316073517052435</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>-0.1162511405443751</v>
+        <v>-0.09254526025634062</v>
       </c>
       <c r="K43" s="20" t="inlineStr">
         <is>
@@ -32482,17 +33890,17 @@
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
-          <t>Tokyo Ohka (JP)</t>
+          <t>Entegris (US)</t>
         </is>
       </c>
       <c r="L45" s="22" t="n">
-        <v>0.02771515714096284</v>
+        <v>0.07046073881615222</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>-0.02022756005056892</v>
+        <v>0.05038497211026383</v>
       </c>
       <c r="N45" s="22" t="n">
-        <v>-0.04000990957512696</v>
+        <v>-0.005499149357600208</v>
       </c>
       <c r="P45" s="20" t="inlineStr">
         <is>
@@ -32546,17 +33954,17 @@
       </c>
       <c r="K46" s="20" t="inlineStr">
         <is>
-          <t>Resonac (JP)</t>
+          <t>Tokyo Ohka (JP)</t>
         </is>
       </c>
       <c r="L46" s="22" t="n">
-        <v>0.04321486268174479</v>
+        <v>0.02771515714096284</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>-0.06918918918918915</v>
+        <v>-0.02022756005056892</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>-0.07052896725440805</v>
+        <v>-0.04000990957512696</v>
       </c>
       <c r="P46" s="20" t="inlineStr">
         <is>
@@ -32604,31 +34012,31 @@
       </c>
       <c r="K47" s="20" t="inlineStr">
         <is>
-          <t>Entegris (US)</t>
+          <t>Resonac (JP)</t>
         </is>
       </c>
       <c r="L47" s="22" t="n">
-        <v>0</v>
+        <v>0.04321486268174479</v>
       </c>
       <c r="M47" s="22" t="n">
-        <v>-0.01875432323476944</v>
+        <v>-0.06918918918918915</v>
       </c>
       <c r="N47" s="22" t="n">
-        <v>-0.0709599945325956</v>
+        <v>-0.07052896725440805</v>
       </c>
       <c r="P47" s="20" t="inlineStr">
         <is>
-          <t>Gold Circuit (TW)</t>
+          <t>Amphenol (US)</t>
         </is>
       </c>
       <c r="Q47" s="22" t="n">
-        <v>-0.03139013452914796</v>
+        <v>0.03905942038695542</v>
       </c>
       <c r="R47" s="22" t="n">
-        <v>-0.08860759493670889</v>
+        <v>-0.0139939563114243</v>
       </c>
       <c r="S47" s="22" t="n">
-        <v>-0.05263157894736847</v>
+        <v>-0.04842442193344576</v>
       </c>
     </row>
     <row r="48">
@@ -32638,13 +34046,13 @@
         </is>
       </c>
       <c r="B48" s="22" t="n">
-        <v>0</v>
+        <v>0.02807839662423306</v>
       </c>
       <c r="C48" s="22" t="n">
-        <v>-0.0244904112257025</v>
+        <v>0.002900333918644638</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>-0.08810562946911338</v>
+        <v>-0.06250109765394185</v>
       </c>
       <c r="F48" s="20" t="inlineStr">
         <is>
@@ -32676,17 +34084,17 @@
       </c>
       <c r="P48" s="20" t="inlineStr">
         <is>
-          <t>Elite Material (TW)</t>
+          <t>Gold Circuit (TW)</t>
         </is>
       </c>
       <c r="Q48" s="22" t="n">
-        <v>-0.06311637080867849</v>
+        <v>-0.03139013452914796</v>
       </c>
       <c r="R48" s="22" t="n">
-        <v>-0.03943377148634986</v>
+        <v>-0.08860759493670889</v>
       </c>
       <c r="S48" s="22" t="n">
-        <v>-0.05378486055776888</v>
+        <v>-0.05263157894736847</v>
       </c>
     </row>
     <row r="49">
@@ -32724,43 +34132,43 @@
         </is>
       </c>
       <c r="L49" s="28" t="n">
-        <v>0.02208785504507106</v>
+        <v>0.03215367487594995</v>
       </c>
       <c r="M49" s="28" t="n">
-        <v>-0.0261326802639672</v>
+        <v>-0.01625563807181959</v>
       </c>
       <c r="N49" s="28" t="n">
-        <v>-0.04069600136687297</v>
+        <v>-0.03134445205615934</v>
       </c>
       <c r="P49" s="20" t="inlineStr">
         <is>
-          <t>TDK (JP)</t>
+          <t>Elite Material (TW)</t>
         </is>
       </c>
       <c r="Q49" s="22" t="n">
-        <v>0.02784761168052596</v>
+        <v>-0.06311637080867849</v>
       </c>
       <c r="R49" s="22" t="n">
-        <v>-0.06227946365561043</v>
+        <v>-0.03943377148634986</v>
       </c>
       <c r="S49" s="22" t="n">
-        <v>-0.06590509666080846</v>
+        <v>-0.05378486055776888</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="20" t="inlineStr">
         <is>
-          <t>Tokyo Electron (JP)</t>
+          <t>Nova (IL)</t>
         </is>
       </c>
       <c r="B50" s="22" t="n">
-        <v>0.03073545554335899</v>
+        <v>0.03562741443949502</v>
       </c>
       <c r="C50" s="22" t="n">
-        <v>-0.06891422905304911</v>
+        <v>0.02365405541072185</v>
       </c>
       <c r="D50" s="22" t="n">
-        <v>-0.1159856900771983</v>
+        <v>-0.1042572491658004</v>
       </c>
       <c r="F50" s="20" t="inlineStr">
         <is>
@@ -32778,33 +34186,33 @@
       </c>
       <c r="P50" s="20" t="inlineStr">
         <is>
-          <t>Taiyo Yuden (JP)</t>
+          <t>TDK (JP)</t>
         </is>
       </c>
       <c r="Q50" s="22" t="n">
-        <v>0.001749883341110703</v>
+        <v>0.02784761168052596</v>
       </c>
       <c r="R50" s="22" t="n">
-        <v>-0.05585486531061024</v>
+        <v>-0.06227946365561043</v>
       </c>
       <c r="S50" s="22" t="n">
-        <v>-0.08405333333333331</v>
+        <v>-0.06590509666080846</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="20" t="inlineStr">
         <is>
-          <t>Nova (IL)</t>
+          <t>Tokyo Electron (JP)</t>
         </is>
       </c>
       <c r="B51" s="22" t="n">
-        <v>0</v>
+        <v>0.03073545554335899</v>
       </c>
       <c r="C51" s="22" t="n">
-        <v>-0.01156145430473499</v>
+        <v>-0.06891422905304911</v>
       </c>
       <c r="D51" s="22" t="n">
-        <v>-0.1350723838080359</v>
+        <v>-0.1159856900771983</v>
       </c>
       <c r="F51" s="20" t="inlineStr">
         <is>
@@ -32827,17 +34235,17 @@
       </c>
       <c r="P51" s="20" t="inlineStr">
         <is>
-          <t>Amphenol (US)</t>
+          <t>Taiyo Yuden (JP)</t>
         </is>
       </c>
       <c r="Q51" s="22" t="n">
-        <v>0</v>
+        <v>0.001749883341110703</v>
       </c>
       <c r="R51" s="22" t="n">
-        <v>-0.05105904018330554</v>
+        <v>-0.05585486531061024</v>
       </c>
       <c r="S51" s="22" t="n">
-        <v>-0.08419522560877346</v>
+        <v>-0.08405333333333331</v>
       </c>
     </row>
     <row r="52">
@@ -32847,13 +34255,13 @@
         </is>
       </c>
       <c r="B52" s="22" t="n">
-        <v>0</v>
+        <v>0.04533287201821889</v>
       </c>
       <c r="C52" s="22" t="n">
-        <v>-0.03588744263115917</v>
+        <v>0.007818548543200299</v>
       </c>
       <c r="D52" s="22" t="n">
-        <v>-0.1614987106914454</v>
+        <v>-0.1234870390561091</v>
       </c>
       <c r="F52" s="20" t="inlineStr">
         <is>
@@ -32911,13 +34319,13 @@
         </is>
       </c>
       <c r="B53" s="22" t="n">
-        <v>0</v>
+        <v>0.02151757376787411</v>
       </c>
       <c r="C53" s="22" t="n">
-        <v>-0.04294042712400581</v>
+        <v>-0.02234682716439651</v>
       </c>
       <c r="D53" s="22" t="n">
-        <v>-0.1829546094936313</v>
+        <v>-0.165373775031709</v>
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
@@ -32939,13 +34347,13 @@
         </is>
       </c>
       <c r="L53" s="31" t="n">
-        <v>0</v>
+        <v>0.01034106868413764</v>
       </c>
       <c r="M53" s="31" t="n">
-        <v>0.03308029996797668</v>
+        <v>0.04376345430617512</v>
       </c>
       <c r="N53" s="31" t="n">
-        <v>0.03579815416394827</v>
+        <v>0.04650941401906072</v>
       </c>
       <c r="P53" s="20" t="inlineStr">
         <is>
@@ -32965,31 +34373,31 @@
     <row r="54">
       <c r="A54" s="20" t="inlineStr">
         <is>
-          <t>KLA (US)</t>
+          <t>Teradyne (US)</t>
         </is>
       </c>
       <c r="B54" s="22" t="n">
-        <v>0</v>
+        <v>0.04750806691191345</v>
       </c>
       <c r="C54" s="22" t="n">
-        <v>-0.07747000342365173</v>
+        <v>-0.03835528031899527</v>
       </c>
       <c r="D54" s="22" t="n">
-        <v>-0.2057382826089199</v>
+        <v>-0.16821714423739</v>
       </c>
       <c r="F54" s="20" t="inlineStr">
         <is>
-          <t>Hon Hai (TW)</t>
+          <t>HPE (US)</t>
         </is>
       </c>
       <c r="G54" s="22" t="n">
-        <v>0.01020408163265296</v>
+        <v>0.03610352329381961</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>0.02484472049689446</v>
+        <v>0.08468532692241126</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>-0.033203125</v>
+        <v>-0.02390504788537373</v>
       </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
@@ -32997,13 +34405,13 @@
         </is>
       </c>
       <c r="L54" s="22" t="n">
-        <v>0</v>
+        <v>0.045307062639663</v>
       </c>
       <c r="M54" s="22" t="n">
-        <v>-0.01760496948777768</v>
+        <v>0.02690446369653321</v>
       </c>
       <c r="N54" s="22" t="n">
-        <v>-0.05613781793359363</v>
+        <v>-0.01337419492750203</v>
       </c>
       <c r="P54" s="20" t="inlineStr">
         <is>
@@ -33023,31 +34431,31 @@
     <row r="55">
       <c r="A55" s="20" t="inlineStr">
         <is>
-          <t>Teradyne (US)</t>
+          <t>KLA (US)</t>
         </is>
       </c>
       <c r="B55" s="22" t="n">
-        <v>0</v>
+        <v>0.02982371656061744</v>
       </c>
       <c r="C55" s="22" t="n">
-        <v>-0.08196915130595273</v>
+        <v>-0.04995673028709147</v>
       </c>
       <c r="D55" s="22" t="n">
-        <v>-0.2059413363615118</v>
+        <v>-0.1820504462744992</v>
       </c>
       <c r="F55" s="20" t="inlineStr">
         <is>
-          <t>Quanta (TW)</t>
+          <t>Hon Hai (TW)</t>
         </is>
       </c>
       <c r="G55" s="22" t="n">
-        <v>0.01708074534161486</v>
+        <v>0.01020408163265296</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>0.02184087363494536</v>
+        <v>0.02484472049689446</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>-0.04099560761346999</v>
+        <v>-0.033203125</v>
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
@@ -33085,41 +34493,41 @@
         </is>
       </c>
       <c r="B56" s="22" t="n">
-        <v>0</v>
+        <v>0.01410528885690798</v>
       </c>
       <c r="C56" s="22" t="n">
-        <v>-0.0985007060338966</v>
+        <v>-0.08578479808820616</v>
       </c>
       <c r="D56" s="22" t="n">
-        <v>-0.2270892965910749</v>
+        <v>-0.2161871678588961</v>
       </c>
       <c r="F56" s="20" t="inlineStr">
         <is>
-          <t>HPE (US)</t>
+          <t>Quanta (TW)</t>
         </is>
       </c>
       <c r="G56" s="22" t="n">
-        <v>0</v>
+        <v>0.01708074534161486</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>0.04688894742307981</v>
+        <v>0.02184087363494536</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>-0.05791754378792513</v>
+        <v>-0.04099560761346999</v>
       </c>
       <c r="K56" s="20" t="inlineStr">
         <is>
-          <t>Sumitomo Electric (JP)</t>
+          <t>Lumentum (US)</t>
         </is>
       </c>
       <c r="L56" s="22" t="n">
-        <v>0.03506787330316752</v>
+        <v>0.05877034412011573</v>
       </c>
       <c r="M56" s="22" t="n">
-        <v>-0.05888403188480329</v>
+        <v>0.05309355800131854</v>
       </c>
       <c r="N56" s="22" t="n">
-        <v>-0.1204037490987744</v>
+        <v>-0.07558165135989192</v>
       </c>
       <c r="P56" s="20" t="inlineStr">
         <is>
@@ -33167,17 +34575,17 @@
       </c>
       <c r="K57" s="20" t="inlineStr">
         <is>
-          <t>Lumentum (US)</t>
+          <t>Arista (US)</t>
         </is>
       </c>
       <c r="L57" s="22" t="n">
-        <v>0</v>
+        <v>0.05506654369412312</v>
       </c>
       <c r="M57" s="22" t="n">
-        <v>-0.0053616784322712</v>
+        <v>0.03206577338875305</v>
       </c>
       <c r="N57" s="22" t="n">
-        <v>-0.1268943697055096</v>
+        <v>-0.08094559945885182</v>
       </c>
       <c r="P57" s="29" t="inlineStr">
         <is>
@@ -33185,13 +34593,13 @@
         </is>
       </c>
       <c r="Q57" s="31" t="n">
-        <v>0</v>
+        <v>0.01497074595668857</v>
       </c>
       <c r="R57" s="31" t="n">
-        <v>-0.1048057995219467</v>
+        <v>-0.0914040745646888</v>
       </c>
       <c r="S57" s="31" t="n">
-        <v>-0.3204577952044204</v>
+        <v>-0.3102845414895777</v>
       </c>
     </row>
     <row r="58">
@@ -33201,13 +34609,13 @@
         </is>
       </c>
       <c r="B58" s="31" t="n">
-        <v>0</v>
+        <v>0.05227730287163324</v>
       </c>
       <c r="C58" s="31" t="n">
-        <v>-0.0732628936145141</v>
+        <v>-0.0248155772216192</v>
       </c>
       <c r="D58" s="31" t="n">
-        <v>-0.2790549376946737</v>
+        <v>-0.2413658743187297</v>
       </c>
       <c r="F58" s="20" t="inlineStr">
         <is>
@@ -33215,27 +34623,27 @@
         </is>
       </c>
       <c r="G58" s="22" t="n">
-        <v>0</v>
+        <v>0.02760452724652573</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>-0.005411646004892412</v>
+        <v>0.02204349531204275</v>
       </c>
       <c r="I58" s="22" t="n">
-        <v>-0.1071093354630567</v>
+        <v>-0.08246151078567809</v>
       </c>
       <c r="K58" s="20" t="inlineStr">
         <is>
-          <t>Arista (US)</t>
+          <t>Sumitomo Electric (JP)</t>
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>0</v>
+        <v>0.03506787330316752</v>
       </c>
       <c r="M58" s="22" t="n">
-        <v>-0.02180030296936253</v>
+        <v>-0.05888403188480329</v>
       </c>
       <c r="N58" s="22" t="n">
-        <v>-0.1289133315485043</v>
+        <v>-0.1204037490987744</v>
       </c>
       <c r="P58" s="26" t="inlineStr">
         <is>
@@ -33243,13 +34651,13 @@
         </is>
       </c>
       <c r="Q58" s="28" t="n">
-        <v>-0.009669402301262319</v>
+        <v>-0.006067391211686053</v>
       </c>
       <c r="R58" s="28" t="n">
-        <v>-0.04086930226931108</v>
+        <v>-0.03750484834736847</v>
       </c>
       <c r="S58" s="28" t="n">
-        <v>-0.07753411942330217</v>
+        <v>-0.07447118226395748</v>
       </c>
     </row>
     <row r="59">
@@ -33259,13 +34667,13 @@
         </is>
       </c>
       <c r="B59" s="28" t="n">
-        <v>0.02406215199613958</v>
+        <v>0.03929940933230031</v>
       </c>
       <c r="C59" s="28" t="n">
-        <v>-0.04841674553896783</v>
+        <v>-0.03401695584697473</v>
       </c>
       <c r="D59" s="28" t="n">
-        <v>-0.09759168822089509</v>
+        <v>-0.08525749971415449</v>
       </c>
       <c r="F59" s="20" t="inlineStr">
         <is>
@@ -33273,27 +34681,27 @@
         </is>
       </c>
       <c r="G59" s="22" t="n">
-        <v>0</v>
+        <v>0.07465369712598746</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>0.0119811049669547</v>
+        <v>0.08752923587438</v>
       </c>
       <c r="I59" s="22" t="n">
-        <v>-0.1504829095906438</v>
+        <v>-0.08706331801987366</v>
       </c>
       <c r="K59" s="20" t="inlineStr">
         <is>
-          <t>Fujikura (JP)</t>
+          <t>Fabrinet (US)</t>
         </is>
       </c>
       <c r="L59" s="22" t="n">
-        <v>0.02865761689291091</v>
+        <v>0.05525151199197098</v>
       </c>
       <c r="M59" s="22" t="n">
-        <v>-0.02385496183206104</v>
+        <v>-0.03451676367738699</v>
       </c>
       <c r="N59" s="22" t="n">
-        <v>-0.1736672051696284</v>
+        <v>-0.1437944711757159</v>
       </c>
     </row>
     <row r="60">
@@ -33303,27 +34711,27 @@
         </is>
       </c>
       <c r="G60" s="22" t="n">
-        <v>0</v>
+        <v>0.07341699684006753</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>0.006775404919467265</v>
+        <v>0.08068983164109755</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>-0.2111486556459593</v>
+        <v>-0.1532335589902356</v>
       </c>
       <c r="K60" s="20" t="inlineStr">
         <is>
-          <t>Fabrinet (US)</t>
+          <t>Fujikura (JP)</t>
         </is>
       </c>
       <c r="L60" s="22" t="n">
-        <v>0</v>
+        <v>0.02865761689291091</v>
       </c>
       <c r="M60" s="22" t="n">
-        <v>-0.08506813271454572</v>
+        <v>-0.02385496183206104</v>
       </c>
       <c r="N60" s="22" t="n">
-        <v>-0.1886242103476857</v>
+        <v>-0.1736672051696284</v>
       </c>
       <c r="P60" s="19" t="inlineStr">
         <is>
@@ -33343,13 +34751,13 @@
         </is>
       </c>
       <c r="G61" s="31" t="n">
-        <v>0</v>
+        <v>0.1211839261629251</v>
       </c>
       <c r="H61" s="31" t="n">
-        <v>-0.1769829093824775</v>
+        <v>-0.07724646704225824</v>
       </c>
       <c r="I61" s="31" t="n">
-        <v>-0.3183451348861954</v>
+        <v>-0.2357395220436455</v>
       </c>
       <c r="K61" s="20" t="inlineStr">
         <is>
@@ -33357,13 +34765,13 @@
         </is>
       </c>
       <c r="L61" s="22" t="n">
-        <v>0</v>
+        <v>0.06451464237531734</v>
       </c>
       <c r="M61" s="22" t="n">
-        <v>-0.04443487021636472</v>
+        <v>0.01721307239795022</v>
       </c>
       <c r="N61" s="22" t="n">
-        <v>-0.2631404008564008</v>
+        <v>-0.2156021673368317</v>
       </c>
       <c r="P61" s="5" t="inlineStr">
         <is>
@@ -33413,13 +34821,13 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>0.01291860923929566</v>
+        <v>0.03511612061725068</v>
       </c>
       <c r="H62" s="28" t="n">
-        <v>-0.0001221039451413164</v>
+        <v>0.02084126410722812</v>
       </c>
       <c r="I62" s="28" t="n">
-        <v>-0.05000017033638408</v>
+        <v>-0.0324934622264525</v>
       </c>
       <c r="K62" s="29" t="inlineStr">
         <is>
@@ -33471,13 +34879,13 @@
         </is>
       </c>
       <c r="L63" s="28" t="n">
-        <v>0.005914802540734598</v>
+        <v>0.03483991989126738</v>
       </c>
       <c r="M63" s="28" t="n">
-        <v>-0.04184994813491004</v>
+        <v>-0.01387862693834121</v>
       </c>
       <c r="N63" s="28" t="n">
-        <v>-0.1359927752675782</v>
+        <v>-0.1114804446687769</v>
       </c>
       <c r="P63" s="20" t="inlineStr">
         <is>
@@ -33570,13 +34978,13 @@
         </is>
       </c>
       <c r="Q65" s="22" t="n">
-        <v>0</v>
+        <v>0.03301784882754877</v>
       </c>
       <c r="R65" s="22" t="n">
-        <v>-0.02633645025721987</v>
+        <v>0.005811825637081824</v>
       </c>
       <c r="S65" s="22" t="n">
-        <v>-0.1523383965042642</v>
+        <v>-0.1243504338231244</v>
       </c>
     </row>
     <row r="66">
@@ -33600,27 +35008,27 @@
         </is>
       </c>
       <c r="G66" s="22" t="n">
-        <v>0</v>
+        <v>0.04421902020388258</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>0.01499037471130271</v>
+        <v>0.05987225459740819</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>0.09991281958456311</v>
+        <v>0.1485498867762824</v>
       </c>
       <c r="P66" s="20" t="inlineStr">
         <is>
-          <t>Auras (TW)</t>
+          <t>Vertiv (US)</t>
         </is>
       </c>
       <c r="Q66" s="22" t="n">
-        <v>-0.01838235294117652</v>
+        <v>0.04394833733579318</v>
       </c>
       <c r="R66" s="22" t="n">
-        <v>-0.043010752688172</v>
+        <v>0.02456278276659329</v>
       </c>
       <c r="S66" s="22" t="n">
-        <v>-0.1630094043887147</v>
+        <v>-0.1616689501489385</v>
       </c>
     </row>
     <row r="67">
@@ -33630,13 +35038,13 @@
         </is>
       </c>
       <c r="B67" s="22" t="n">
-        <v>0</v>
+        <v>0.04750806691191345</v>
       </c>
       <c r="C67" s="22" t="n">
-        <v>-0.08196915130595273</v>
+        <v>-0.03835528031899527</v>
       </c>
       <c r="D67" s="22" t="n">
-        <v>-0.2059413363615118</v>
+        <v>-0.16821714423739</v>
       </c>
       <c r="F67" s="20" t="inlineStr">
         <is>
@@ -33644,27 +35052,27 @@
         </is>
       </c>
       <c r="G67" s="22" t="n">
-        <v>0</v>
+        <v>0.06490353624801748</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>0.00719047846205223</v>
+        <v>0.072560702189572</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>0.04231782731507416</v>
+        <v>0.1099679402021729</v>
       </c>
       <c r="P67" s="20" t="inlineStr">
         <is>
-          <t>Fortune Electric (TW)</t>
+          <t>Auras (TW)</t>
         </is>
       </c>
       <c r="Q67" s="22" t="n">
-        <v>-0.04878048780487809</v>
+        <v>-0.01838235294117652</v>
       </c>
       <c r="R67" s="22" t="n">
-        <v>-0.07290015847860543</v>
+        <v>-0.043010752688172</v>
       </c>
       <c r="S67" s="22" t="n">
-        <v>-0.1690340909090909</v>
+        <v>-0.1630094043887147</v>
       </c>
     </row>
     <row r="68">
@@ -33674,13 +35082,13 @@
         </is>
       </c>
       <c r="B68" s="31" t="n">
-        <v>0</v>
+        <v>0.08503116372304897</v>
       </c>
       <c r="C68" s="31" t="n">
-        <v>-0.1172661702681402</v>
+        <v>-0.04220628546833638</v>
       </c>
       <c r="D68" s="31" t="n">
-        <v>-0.3096398802705889</v>
+        <v>-0.2509377559020135</v>
       </c>
       <c r="F68" s="20" t="inlineStr">
         <is>
@@ -33688,27 +35096,27 @@
         </is>
       </c>
       <c r="G68" s="22" t="n">
-        <v>0</v>
+        <v>0.01455115250139616</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>0.01035921727229239</v>
+        <v>0.02506110832401265</v>
       </c>
       <c r="I68" s="22" t="n">
-        <v>-0.3283918458528267</v>
+        <v>-0.31861917318065</v>
       </c>
       <c r="P68" s="20" t="inlineStr">
         <is>
-          <t>Vertiv (US)</t>
+          <t>Fortune Electric (TW)</t>
         </is>
       </c>
       <c r="Q68" s="22" t="n">
-        <v>0</v>
+        <v>-0.04878048780487809</v>
       </c>
       <c r="R68" s="22" t="n">
-        <v>-0.01856945777477137</v>
+        <v>-0.07290015847860543</v>
       </c>
       <c r="S68" s="22" t="n">
-        <v>-0.1969611714785398</v>
+        <v>-0.1690340909090909</v>
       </c>
     </row>
     <row r="69">
@@ -33718,13 +35126,13 @@
         </is>
       </c>
       <c r="B69" s="28" t="n">
-        <v>0.02269694304576718</v>
+        <v>0.04478681481826091</v>
       </c>
       <c r="C69" s="28" t="n">
-        <v>-0.0304029072571419</v>
+        <v>-0.01062394795934835</v>
       </c>
       <c r="D69" s="28" t="n">
-        <v>-0.1244229069820515</v>
+        <v>-0.1083518542332686</v>
       </c>
       <c r="F69" s="26" t="inlineStr">
         <is>
@@ -33732,13 +35140,13 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>0</v>
+        <v>0.04122456965109874</v>
       </c>
       <c r="H69" s="28" t="n">
-        <v>0.01084669014854911</v>
+        <v>0.05249802170366428</v>
       </c>
       <c r="I69" s="28" t="n">
-        <v>-0.06205373298439646</v>
+        <v>-0.02003378206739822</v>
       </c>
       <c r="P69" s="29" t="inlineStr">
         <is>
@@ -33762,13 +35170,13 @@
         </is>
       </c>
       <c r="Q70" s="28" t="n">
-        <v>-0.006399421775616823</v>
+        <v>0.00322135149480092</v>
       </c>
       <c r="R70" s="28" t="n">
-        <v>-0.03328599310928913</v>
+        <v>-0.02387592855483084</v>
       </c>
       <c r="S70" s="28" t="n">
-        <v>-0.1607337387828238</v>
+        <v>-0.1528237157814812</v>
       </c>
     </row>
   </sheetData>
